--- a/research/traditional_assets/database/data/jordan/jordan_steel.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_steel.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="ase_aspmm" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,112 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0917</v>
+        <v>-0.0742</v>
+      </c>
+      <c r="E2">
+        <v>-0.0268</v>
       </c>
       <c r="G2">
-        <v>-0.02242774566473988</v>
+        <v>0.03383050847457627</v>
       </c>
       <c r="H2">
-        <v>-0.02242774566473988</v>
+        <v>0.03383050847457627</v>
       </c>
       <c r="I2">
-        <v>-0.02011560693641619</v>
+        <v>0.01019209039548022</v>
       </c>
       <c r="J2">
-        <v>-0.02011560693641619</v>
+        <v>0.009952037168600651</v>
       </c>
       <c r="K2">
-        <v>-0.76</v>
+        <v>-1.964</v>
       </c>
       <c r="L2">
-        <v>-0.08786127167630058</v>
+        <v>-0.04438418079096045</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01806930693069307</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.260183299389002</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.511</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.01806930693069307</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>-0.260183299389002</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>1.864</v>
+        <v>0.253</v>
       </c>
       <c r="V2">
-        <v>0.1947753396029258</v>
+        <v>0.008946251768033946</v>
       </c>
       <c r="W2">
-        <v>-0.08887138130686519</v>
+        <v>-0.07021943573667712</v>
       </c>
       <c r="X2">
-        <v>0.1520962249708595</v>
+        <v>0.3061753184357731</v>
       </c>
       <c r="Y2">
-        <v>-0.2409676062777247</v>
+        <v>-0.3763947541724502</v>
       </c>
       <c r="Z2">
-        <v>0.5224060876917502</v>
+        <v>0.4897349344253223</v>
       </c>
       <c r="AA2">
-        <v>-0.01012328701558102</v>
+        <v>-0.02130206956602864</v>
       </c>
       <c r="AB2">
-        <v>0.1115245840047897</v>
+        <v>0.1940107958447419</v>
       </c>
       <c r="AC2">
-        <v>-0.1216478710203708</v>
+        <v>-0.220379844236011</v>
       </c>
       <c r="AD2">
-        <v>5.79</v>
+        <v>43.36</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>5.79</v>
+        <v>43.36</v>
       </c>
       <c r="AG2">
-        <v>3.926</v>
+        <v>43.107</v>
       </c>
       <c r="AH2">
-        <v>0.376953125</v>
+        <v>0.605248464544947</v>
       </c>
       <c r="AI2">
-        <v>0.3824306472919419</v>
+        <v>0.4661363147710169</v>
       </c>
       <c r="AJ2">
-        <v>0.290901007705987</v>
+        <v>0.6038494403742978</v>
       </c>
       <c r="AK2">
-        <v>0.2957216028924375</v>
+        <v>0.464680328133927</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>3.104</v>
       </c>
       <c r="AM2">
-        <v>-0.042</v>
+        <v>3.053</v>
       </c>
       <c r="AN2">
-        <v>17.07964601769912</v>
+        <v>21.43351458230351</v>
+      </c>
+      <c r="AO2">
+        <v>0.1452963917525773</v>
       </c>
       <c r="AP2">
-        <v>11.5811209439528</v>
+        <v>21.30845279288186</v>
       </c>
       <c r="AQ2">
-        <v>4.142857142857143</v>
+        <v>0.1477235506059613</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Steel Industry Co. Ltd. (ASE:NAST)</t>
+          <t>Arabian Steel Pipes Manufacturing CO. LTD (ASE:ASPMM)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -713,109 +724,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.136</v>
+        <v>0.0177</v>
+      </c>
+      <c r="E3">
+        <v>-0.0268</v>
       </c>
       <c r="G3">
-        <v>0.08987138263665596</v>
+        <v>0.100709219858156</v>
       </c>
       <c r="H3">
-        <v>0.08987138263665596</v>
+        <v>0.100709219858156</v>
       </c>
       <c r="I3">
-        <v>0.02443729903536978</v>
+        <v>0.1418439716312057</v>
       </c>
       <c r="J3">
-        <v>0.02443729903536978</v>
+        <v>0.1318214634560666</v>
       </c>
       <c r="K3">
-        <v>-0.231</v>
+        <v>1.55</v>
       </c>
       <c r="L3">
-        <v>-0.03713826366559486</v>
+        <v>0.1099290780141844</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.508</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04341880341880342</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.327741935483871</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.508</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.04341880341880342</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>0.327741935483871</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>1.8</v>
+        <v>0.116</v>
       </c>
       <c r="V3">
-        <v>0.3163444639718805</v>
+        <v>0.009914529914529915</v>
       </c>
       <c r="W3">
-        <v>-0.03553846153846154</v>
+        <v>0.08611111111111111</v>
       </c>
       <c r="X3">
-        <v>0.135937486221969</v>
+        <v>0.2181578330817627</v>
       </c>
       <c r="Y3">
-        <v>-0.1714759477604305</v>
+        <v>-0.1320467219706516</v>
       </c>
       <c r="Z3">
-        <v>0.7615083251714004</v>
+        <v>0.7217444717444716</v>
       </c>
       <c r="AA3">
-        <v>0.01860920666013712</v>
+        <v>0.09514141250668197</v>
       </c>
       <c r="AB3">
-        <v>0.1101661180437023</v>
+        <v>0.185152995751041</v>
       </c>
       <c r="AC3">
-        <v>-0.09155691138356514</v>
+        <v>-0.09001158324435908</v>
       </c>
       <c r="AD3">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.41</v>
+        <v>3.74</v>
       </c>
       <c r="AG3">
-        <v>0.6100000000000001</v>
+        <v>3.624</v>
       </c>
       <c r="AH3">
-        <v>0.2975308641975308</v>
+        <v>0.2422279792746114</v>
       </c>
       <c r="AI3">
-        <v>0.2812135355892649</v>
+        <v>0.1637478108581436</v>
       </c>
       <c r="AJ3">
-        <v>0.09682539682539683</v>
+        <v>0.2364917776037588</v>
       </c>
       <c r="AK3">
-        <v>0.09010339734121123</v>
+        <v>0.1594789649709558</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>0.039</v>
       </c>
       <c r="AN3">
-        <v>4.538606403013183</v>
+        <v>1.520325203252033</v>
+      </c>
+      <c r="AO3">
+        <v>22.22222222222222</v>
       </c>
       <c r="AP3">
-        <v>1.148775894538607</v>
+        <v>1.473170731707317</v>
+      </c>
+      <c r="AQ3">
+        <v>51.28205128205128</v>
       </c>
     </row>
     <row r="4">
@@ -826,7 +849,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Jordan Pipes Manufacturing Co. Ltd. (ASE:JOPI)</t>
+          <t>Jordan Steel P.L.C. (ASE:JOST)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -835,25 +858,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.0474</v>
+        <v>-0.0742</v>
       </c>
       <c r="G4">
-        <v>-0.3098765432098765</v>
+        <v>0.004275862068965517</v>
       </c>
       <c r="H4">
-        <v>-0.3098765432098765</v>
+        <v>0.004275862068965517</v>
       </c>
       <c r="I4">
-        <v>-0.1341563786008231</v>
+        <v>-0.04724137931034483</v>
       </c>
       <c r="J4">
-        <v>-0.1341563786008231</v>
+        <v>-0.04724137931034483</v>
       </c>
       <c r="K4">
-        <v>-0.529</v>
+        <v>-3.29</v>
       </c>
       <c r="L4">
-        <v>-0.2176954732510288</v>
+        <v>-0.113448275862069</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,70 +900,8916 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0.064</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="V4">
-        <v>0.01649484536082474</v>
+        <v>0.006640625</v>
       </c>
       <c r="W4">
-        <v>-0.1422043010752688</v>
+        <v>-0.1064724919093851</v>
       </c>
       <c r="X4">
-        <v>0.16825496371975</v>
+        <v>0.4985402596796562</v>
       </c>
       <c r="Y4">
-        <v>-0.3104592647950188</v>
+        <v>-0.6050127515890413</v>
       </c>
       <c r="Z4">
-        <v>0.2896305125148987</v>
+        <v>0.4509197207407523</v>
       </c>
       <c r="AA4">
-        <v>-0.03885578069129916</v>
+        <v>-0.02130206956602864</v>
       </c>
       <c r="AB4">
-        <v>0.1128830499658772</v>
+        <v>0.1990777746699824</v>
       </c>
       <c r="AC4">
-        <v>-0.1517388306571764</v>
+        <v>-0.220379844236011</v>
       </c>
       <c r="AD4">
-        <v>3.38</v>
+        <v>35.5</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>3.38</v>
+        <v>35.5</v>
       </c>
       <c r="AG4">
-        <v>3.316</v>
+        <v>35.415</v>
       </c>
       <c r="AH4">
-        <v>0.465564738292011</v>
+        <v>0.7349896480331264</v>
       </c>
       <c r="AI4">
-        <v>0.5144596651445966</v>
+        <v>0.5625990491283677</v>
       </c>
       <c r="AJ4">
-        <v>0.4608115619788771</v>
+        <v>0.7345224515192367</v>
       </c>
       <c r="AK4">
-        <v>0.5096833691976637</v>
+        <v>0.5620090454653653</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AM4">
-        <v>-0.042</v>
+        <v>2.81</v>
       </c>
       <c r="AN4">
-        <v>-17.60416666666666</v>
+        <v>-109.5679012345679</v>
+      </c>
+      <c r="AO4">
+        <v>-0.4875444839857652</v>
       </c>
       <c r="AP4">
-        <v>-17.27083333333333</v>
+        <v>-109.3055555555555</v>
       </c>
       <c r="AQ4">
-        <v>7.761904761904762</v>
+        <v>-0.4875444839857652</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>The Jordan Pipes Manufacturing Co. Ltd. (ASE:JOPI)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.14</v>
+      </c>
+      <c r="G5">
+        <v>-0.04086956521739131</v>
+      </c>
+      <c r="H5">
+        <v>-0.04086956521739131</v>
+      </c>
+      <c r="I5">
+        <v>-0.1556521739130435</v>
+      </c>
+      <c r="J5">
+        <v>-0.1556521739130435</v>
+      </c>
+      <c r="K5">
+        <v>-0.224</v>
+      </c>
+      <c r="L5">
+        <v>-0.1947826086956522</v>
+      </c>
+      <c r="M5">
+        <v>0.003</v>
+      </c>
+      <c r="N5">
+        <v>0.0007936507936507938</v>
+      </c>
+      <c r="O5">
+        <v>-0.01339285714285714</v>
+      </c>
+      <c r="P5">
+        <v>0.003</v>
+      </c>
+      <c r="Q5">
+        <v>0.0007936507936507938</v>
+      </c>
+      <c r="R5">
+        <v>-0.01339285714285714</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0.052</v>
+      </c>
+      <c r="V5">
+        <v>0.01375661375661376</v>
+      </c>
+      <c r="W5">
+        <v>-0.07021943573667712</v>
+      </c>
+      <c r="X5">
+        <v>0.3061753184357731</v>
+      </c>
+      <c r="Y5">
+        <v>-0.3763947541724502</v>
+      </c>
+      <c r="Z5">
+        <v>0.1767599139256071</v>
+      </c>
+      <c r="AA5">
+        <v>-0.02751306486320319</v>
+      </c>
+      <c r="AB5">
+        <v>0.1940107958447419</v>
+      </c>
+      <c r="AC5">
+        <v>-0.2215238607079451</v>
+      </c>
+      <c r="AD5">
+        <v>4.12</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>4.12</v>
+      </c>
+      <c r="AG5">
+        <v>4.068000000000001</v>
+      </c>
+      <c r="AH5">
+        <v>0.5215189873417722</v>
+      </c>
+      <c r="AI5">
+        <v>0.5819209039548022</v>
+      </c>
+      <c r="AJ5">
+        <v>0.518348623853211</v>
+      </c>
+      <c r="AK5">
+        <v>0.578827546955037</v>
+      </c>
+      <c r="AL5">
+        <v>0.204</v>
+      </c>
+      <c r="AM5">
+        <v>0.204</v>
+      </c>
+      <c r="AN5">
+        <v>-36.46017699115044</v>
+      </c>
+      <c r="AO5">
+        <v>-0.8774509803921569</v>
+      </c>
+      <c r="AP5">
+        <v>-36</v>
+      </c>
+      <c r="AQ5">
+        <v>-0.8774509803921569</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Arabian Steel Pipes Manufacturing CO. LTD (ASE:ASPMM)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASE:ASPMM</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Steel</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.242227979274611</v>
+      </c>
+      <c r="F2">
+        <v>0.52</v>
+      </c>
+      <c r="G2">
+        <v>11.7</v>
+      </c>
+      <c r="H2">
+        <v>9.248886508754721</v>
+      </c>
+      <c r="I2">
+        <v>15.324</v>
+      </c>
+      <c r="J2">
+        <v>17.1616865087547</v>
+      </c>
+      <c r="K2">
+        <v>3.74</v>
+      </c>
+      <c r="L2">
+        <v>8.0288</v>
+      </c>
+      <c r="M2">
+        <v>0.185152995751041</v>
+      </c>
+      <c r="N2">
+        <v>0.169481405102283</v>
+      </c>
+      <c r="O2">
+        <v>0.0819025688073395</v>
+      </c>
+      <c r="P2">
+        <v>0.044</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.218157833081763</v>
+      </c>
+      <c r="T2">
+        <v>0.305419593963089</v>
+      </c>
+      <c r="U2">
+        <v>1.31073996818661</v>
+      </c>
+      <c r="V2">
+        <v>1.94844547408083</v>
+      </c>
+      <c r="W2">
+        <v>4.529149606869813</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>11.7</v>
+      </c>
+      <c r="AB2">
+        <v>0.1368370824381754</v>
+      </c>
+      <c r="AC2">
+        <v>0.1023782110091743</v>
+      </c>
+      <c r="AD2">
+        <v>0.2</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>2.46</v>
+      </c>
+      <c r="AH2">
+        <v>0.46</v>
+      </c>
+      <c r="AI2">
+        <v>0.5839999999999996</v>
+      </c>
+      <c r="AJ2">
+        <v>3.74</v>
+      </c>
+      <c r="AK2">
+        <v>3.74</v>
+      </c>
+      <c r="AL2">
+        <v>0.09</v>
+      </c>
+      <c r="AM2">
+        <v>3.740000000000001</v>
+      </c>
+      <c r="AN2">
+        <v>0.116</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1816319253373689</v>
+      </c>
+      <c r="C2">
+        <v>15.81776486518449</v>
+      </c>
+      <c r="D2">
+        <v>15.70176486518449</v>
+      </c>
+      <c r="E2">
+        <v>-3.74</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.116</v>
+      </c>
+      <c r="H2">
+        <v>11.7</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.46</v>
+      </c>
+      <c r="K2">
+        <v>0.46</v>
+      </c>
+      <c r="L2">
+        <v>2</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>2</v>
+      </c>
+      <c r="O2">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="P2">
+        <v>1.6</v>
+      </c>
+      <c r="Q2">
+        <v>2.06</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1816319253373689</v>
+      </c>
+      <c r="T2">
+        <v>1.043810075400446</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2</v>
+      </c>
+      <c r="W2">
+        <v>0.03656</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1813238614866942</v>
+      </c>
+      <c r="C3">
+        <v>15.69730406733843</v>
+      </c>
+      <c r="D3">
+        <v>15.73570406733844</v>
+      </c>
+      <c r="E3">
+        <v>-3.5856</v>
+      </c>
+      <c r="F3">
+        <v>0.1544</v>
+      </c>
+      <c r="G3">
+        <v>0.116</v>
+      </c>
+      <c r="H3">
+        <v>11.7</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.46</v>
+      </c>
+      <c r="K3">
+        <v>0.46</v>
+      </c>
+      <c r="L3">
+        <v>2</v>
+      </c>
+      <c r="M3">
+        <v>0.007056080000000001</v>
+      </c>
+      <c r="N3">
+        <v>1.99294392</v>
+      </c>
+      <c r="O3">
+        <v>0.3985887839999999</v>
+      </c>
+      <c r="P3">
+        <v>1.594355136</v>
+      </c>
+      <c r="Q3">
+        <v>2.054355136</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1827861227138325</v>
+      </c>
+      <c r="T3">
+        <v>1.052244904292571</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2</v>
+      </c>
+      <c r="W3">
+        <v>0.03656</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>283.4434983730343</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1810157976360194</v>
+      </c>
+      <c r="C4">
+        <v>15.57699030577778</v>
+      </c>
+      <c r="D4">
+        <v>15.76979030577778</v>
+      </c>
+      <c r="E4">
+        <v>-3.4312</v>
+      </c>
+      <c r="F4">
+        <v>0.3088</v>
+      </c>
+      <c r="G4">
+        <v>0.116</v>
+      </c>
+      <c r="H4">
+        <v>11.7</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.46</v>
+      </c>
+      <c r="K4">
+        <v>0.46</v>
+      </c>
+      <c r="L4">
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <v>0.01411216</v>
+      </c>
+      <c r="N4">
+        <v>1.98588784</v>
+      </c>
+      <c r="O4">
+        <v>0.3971775679999999</v>
+      </c>
+      <c r="P4">
+        <v>1.588710272</v>
+      </c>
+      <c r="Q4">
+        <v>2.048710272</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1839638751387953</v>
+      </c>
+      <c r="T4">
+        <v>1.060851872549841</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2</v>
+      </c>
+      <c r="W4">
+        <v>0.03656</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>141.7217491865171</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1807077337853447</v>
+      </c>
+      <c r="C5">
+        <v>15.45682453809438</v>
+      </c>
+      <c r="D5">
+        <v>15.80402453809438</v>
+      </c>
+      <c r="E5">
+        <v>-3.2768</v>
+      </c>
+      <c r="F5">
+        <v>0.4631999999999999</v>
+      </c>
+      <c r="G5">
+        <v>0.116</v>
+      </c>
+      <c r="H5">
+        <v>11.7</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.46</v>
+      </c>
+      <c r="K5">
+        <v>0.46</v>
+      </c>
+      <c r="L5">
+        <v>2</v>
+      </c>
+      <c r="M5">
+        <v>0.02116824</v>
+      </c>
+      <c r="N5">
+        <v>1.97883176</v>
+      </c>
+      <c r="O5">
+        <v>0.3957663519999999</v>
+      </c>
+      <c r="P5">
+        <v>1.583065408</v>
+      </c>
+      <c r="Q5">
+        <v>2.043065408</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.185165911118912</v>
+      </c>
+      <c r="T5">
+        <v>1.069636304070148</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2</v>
+      </c>
+      <c r="W5">
+        <v>0.03656</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>94.48116612434478</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.18039966993467</v>
+      </c>
+      <c r="C6">
+        <v>15.33680773021347</v>
+      </c>
+      <c r="D6">
+        <v>15.83840773021347</v>
+      </c>
+      <c r="E6">
+        <v>-3.1224</v>
+      </c>
+      <c r="F6">
+        <v>0.6176</v>
+      </c>
+      <c r="G6">
+        <v>0.116</v>
+      </c>
+      <c r="H6">
+        <v>11.7</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.46</v>
+      </c>
+      <c r="K6">
+        <v>0.46</v>
+      </c>
+      <c r="L6">
+        <v>2</v>
+      </c>
+      <c r="M6">
+        <v>0.02822432</v>
+      </c>
+      <c r="N6">
+        <v>1.97177568</v>
+      </c>
+      <c r="O6">
+        <v>0.3943551359999999</v>
+      </c>
+      <c r="P6">
+        <v>1.577420544</v>
+      </c>
+      <c r="Q6">
+        <v>2.037420544</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1863929895152812</v>
+      </c>
+      <c r="T6">
+        <v>1.078603744580461</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2</v>
+      </c>
+      <c r="W6">
+        <v>0.03656</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>70.86087459325857</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1800916060839952</v>
+      </c>
+      <c r="C7">
+        <v>15.21694085648444</v>
+      </c>
+      <c r="D7">
+        <v>15.87294085648444</v>
+      </c>
+      <c r="E7">
+        <v>-2.968</v>
+      </c>
+      <c r="F7">
+        <v>0.772</v>
+      </c>
+      <c r="G7">
+        <v>0.116</v>
+      </c>
+      <c r="H7">
+        <v>11.7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.46</v>
+      </c>
+      <c r="K7">
+        <v>0.46</v>
+      </c>
+      <c r="L7">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>0.0352804</v>
+      </c>
+      <c r="N7">
+        <v>1.9647196</v>
+      </c>
+      <c r="O7">
+        <v>0.3929439199999999</v>
+      </c>
+      <c r="P7">
+        <v>1.57177568</v>
+      </c>
+      <c r="Q7">
+        <v>2.03177568</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1876459011410476</v>
+      </c>
+      <c r="T7">
+        <v>1.087759973312044</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2</v>
+      </c>
+      <c r="W7">
+        <v>0.03656</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>56.68869967460686</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1797835422333204</v>
+      </c>
+      <c r="C8">
+        <v>15.09722489977291</v>
+      </c>
+      <c r="D8">
+        <v>15.9076248997729</v>
+      </c>
+      <c r="E8">
+        <v>-2.8136</v>
+      </c>
+      <c r="F8">
+        <v>0.9263999999999999</v>
+      </c>
+      <c r="G8">
+        <v>0.116</v>
+      </c>
+      <c r="H8">
+        <v>11.7</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.46</v>
+      </c>
+      <c r="K8">
+        <v>0.46</v>
+      </c>
+      <c r="L8">
+        <v>2</v>
+      </c>
+      <c r="M8">
+        <v>0.04233648</v>
+      </c>
+      <c r="N8">
+        <v>1.95766352</v>
+      </c>
+      <c r="O8">
+        <v>0.391532704</v>
+      </c>
+      <c r="P8">
+        <v>1.566130816</v>
+      </c>
+      <c r="Q8">
+        <v>2.026130816</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1889254704609792</v>
+      </c>
+      <c r="T8">
+        <v>1.097111015420894</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2</v>
+      </c>
+      <c r="W8">
+        <v>0.03656</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>47.24058306217239</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1794754783826457</v>
+      </c>
+      <c r="C9">
+        <v>14.97766085155395</v>
+      </c>
+      <c r="D9">
+        <v>15.94246085155395</v>
+      </c>
+      <c r="E9">
+        <v>-2.6592</v>
+      </c>
+      <c r="F9">
+        <v>1.0808</v>
+      </c>
+      <c r="G9">
+        <v>0.116</v>
+      </c>
+      <c r="H9">
+        <v>11.7</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.46</v>
+      </c>
+      <c r="K9">
+        <v>0.46</v>
+      </c>
+      <c r="L9">
+        <v>2</v>
+      </c>
+      <c r="M9">
+        <v>0.04939256</v>
+      </c>
+      <c r="N9">
+        <v>1.95060744</v>
+      </c>
+      <c r="O9">
+        <v>0.3901214879999999</v>
+      </c>
+      <c r="P9">
+        <v>1.560485952</v>
+      </c>
+      <c r="Q9">
+        <v>2.020485952</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1902325574006943</v>
+      </c>
+      <c r="T9">
+        <v>1.106663155209505</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2</v>
+      </c>
+      <c r="W9">
+        <v>0.03656</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>40.4919283390049</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.179167414531971</v>
+      </c>
+      <c r="C10">
+        <v>14.85824971200662</v>
+      </c>
+      <c r="D10">
+        <v>15.97744971200662</v>
+      </c>
+      <c r="E10">
+        <v>-2.5048</v>
+      </c>
+      <c r="F10">
+        <v>1.2352</v>
+      </c>
+      <c r="G10">
+        <v>0.116</v>
+      </c>
+      <c r="H10">
+        <v>11.7</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.46</v>
+      </c>
+      <c r="K10">
+        <v>0.46</v>
+      </c>
+      <c r="L10">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>0.05644864000000001</v>
+      </c>
+      <c r="N10">
+        <v>1.94355136</v>
+      </c>
+      <c r="O10">
+        <v>0.3887102719999999</v>
+      </c>
+      <c r="P10">
+        <v>1.554841088</v>
+      </c>
+      <c r="Q10">
+        <v>2.014841088</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1915680592738815</v>
+      </c>
+      <c r="T10">
+        <v>1.116422950210912</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2</v>
+      </c>
+      <c r="W10">
+        <v>0.03656</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>35.43043729662929</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1788593506812962</v>
+      </c>
+      <c r="C11">
+        <v>14.73899249010961</v>
+      </c>
+      <c r="D11">
+        <v>16.01259249010961</v>
+      </c>
+      <c r="E11">
+        <v>-2.3504</v>
+      </c>
+      <c r="F11">
+        <v>1.3896</v>
+      </c>
+      <c r="G11">
+        <v>0.116</v>
+      </c>
+      <c r="H11">
+        <v>11.7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.46</v>
+      </c>
+      <c r="K11">
+        <v>0.46</v>
+      </c>
+      <c r="L11">
+        <v>2</v>
+      </c>
+      <c r="M11">
+        <v>0.06350472</v>
+      </c>
+      <c r="N11">
+        <v>1.93649528</v>
+      </c>
+      <c r="O11">
+        <v>0.3872990559999999</v>
+      </c>
+      <c r="P11">
+        <v>1.549196224</v>
+      </c>
+      <c r="Q11">
+        <v>2.009196224</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1929329128365893</v>
+      </c>
+      <c r="T11">
+        <v>1.12639724620136</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2</v>
+      </c>
+      <c r="W11">
+        <v>0.03656</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>31.49372204144825</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1785512868306215</v>
+      </c>
+      <c r="C12">
+        <v>14.6198902037383</v>
+      </c>
+      <c r="D12">
+        <v>16.0478902037383</v>
+      </c>
+      <c r="E12">
+        <v>-2.196</v>
+      </c>
+      <c r="F12">
+        <v>1.544</v>
+      </c>
+      <c r="G12">
+        <v>0.116</v>
+      </c>
+      <c r="H12">
+        <v>11.7</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.46</v>
+      </c>
+      <c r="K12">
+        <v>0.46</v>
+      </c>
+      <c r="L12">
+        <v>2</v>
+      </c>
+      <c r="M12">
+        <v>0.07056080000000001</v>
+      </c>
+      <c r="N12">
+        <v>1.9294392</v>
+      </c>
+      <c r="O12">
+        <v>0.3858878399999999</v>
+      </c>
+      <c r="P12">
+        <v>1.54355136</v>
+      </c>
+      <c r="Q12">
+        <v>2.00355136</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1943280964784684</v>
+      </c>
+      <c r="T12">
+        <v>1.136593193213819</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2</v>
+      </c>
+      <c r="W12">
+        <v>0.03656</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>28.34434983730343</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1782432229799468</v>
+      </c>
+      <c r="C13">
+        <v>14.50094387976299</v>
+      </c>
+      <c r="D13">
+        <v>16.08334387976299</v>
+      </c>
+      <c r="E13">
+        <v>-2.0416</v>
+      </c>
+      <c r="F13">
+        <v>1.6984</v>
+      </c>
+      <c r="G13">
+        <v>0.116</v>
+      </c>
+      <c r="H13">
+        <v>11.7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.46</v>
+      </c>
+      <c r="K13">
+        <v>0.46</v>
+      </c>
+      <c r="L13">
+        <v>2</v>
+      </c>
+      <c r="M13">
+        <v>0.07761688</v>
+      </c>
+      <c r="N13">
+        <v>1.92238312</v>
+      </c>
+      <c r="O13">
+        <v>0.3844766239999999</v>
+      </c>
+      <c r="P13">
+        <v>1.537906496</v>
+      </c>
+      <c r="Q13">
+        <v>1.997906496</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1957546325617379</v>
+      </c>
+      <c r="T13">
+        <v>1.147018262631052</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2</v>
+      </c>
+      <c r="W13">
+        <v>0.03656</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>25.76759076118494</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1779351591292721</v>
+      </c>
+      <c r="C14">
+        <v>14.38215455414847</v>
+      </c>
+      <c r="D14">
+        <v>16.11895455414847</v>
+      </c>
+      <c r="E14">
+        <v>-1.8872</v>
+      </c>
+      <c r="F14">
+        <v>1.8528</v>
+      </c>
+      <c r="G14">
+        <v>0.116</v>
+      </c>
+      <c r="H14">
+        <v>11.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.46</v>
+      </c>
+      <c r="K14">
+        <v>0.46</v>
+      </c>
+      <c r="L14">
+        <v>2</v>
+      </c>
+      <c r="M14">
+        <v>0.08467295999999999</v>
+      </c>
+      <c r="N14">
+        <v>1.91532704</v>
+      </c>
+      <c r="O14">
+        <v>0.3830654079999999</v>
+      </c>
+      <c r="P14">
+        <v>1.532261632</v>
+      </c>
+      <c r="Q14">
+        <v>1.992261632</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1972135899196273</v>
+      </c>
+      <c r="T14">
+        <v>1.157680265444131</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2</v>
+      </c>
+      <c r="W14">
+        <v>0.03656</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>23.6202915310862</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1776270952785973</v>
+      </c>
+      <c r="C15">
+        <v>14.263523272055</v>
+      </c>
+      <c r="D15">
+        <v>16.154723272055</v>
+      </c>
+      <c r="E15">
+        <v>-1.7328</v>
+      </c>
+      <c r="F15">
+        <v>2.0072</v>
+      </c>
+      <c r="G15">
+        <v>0.116</v>
+      </c>
+      <c r="H15">
+        <v>11.7</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.46</v>
+      </c>
+      <c r="K15">
+        <v>0.46</v>
+      </c>
+      <c r="L15">
+        <v>2</v>
+      </c>
+      <c r="M15">
+        <v>0.09172904000000001</v>
+      </c>
+      <c r="N15">
+        <v>1.90827096</v>
+      </c>
+      <c r="O15">
+        <v>0.3816541919999999</v>
+      </c>
+      <c r="P15">
+        <v>1.526616768</v>
+      </c>
+      <c r="Q15">
+        <v>1.986616768</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1987060865271233</v>
+      </c>
+      <c r="T15">
+        <v>1.168587371770154</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2</v>
+      </c>
+      <c r="W15">
+        <v>0.03656</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>21.80334602869495</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1773190314279226</v>
+      </c>
+      <c r="C16">
+        <v>14.14505108794046</v>
+      </c>
+      <c r="D16">
+        <v>16.19065108794046</v>
+      </c>
+      <c r="E16">
+        <v>-1.5784</v>
+      </c>
+      <c r="F16">
+        <v>2.1616</v>
+      </c>
+      <c r="G16">
+        <v>0.116</v>
+      </c>
+      <c r="H16">
+        <v>11.7</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.46</v>
+      </c>
+      <c r="K16">
+        <v>0.46</v>
+      </c>
+      <c r="L16">
+        <v>2</v>
+      </c>
+      <c r="M16">
+        <v>0.09878512</v>
+      </c>
+      <c r="N16">
+        <v>1.90121488</v>
+      </c>
+      <c r="O16">
+        <v>0.3802429759999999</v>
+      </c>
+      <c r="P16">
+        <v>1.520971904</v>
+      </c>
+      <c r="Q16">
+        <v>1.980971904</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.2002332923580495</v>
+      </c>
+      <c r="T16">
+        <v>1.179748131731667</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2</v>
+      </c>
+      <c r="W16">
+        <v>0.03656</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>20.24596416950245</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1770109675772478</v>
+      </c>
+      <c r="C17">
+        <v>14.02673906566404</v>
+      </c>
+      <c r="D17">
+        <v>16.22673906566404</v>
+      </c>
+      <c r="E17">
+        <v>-1.424</v>
+      </c>
+      <c r="F17">
+        <v>2.316</v>
+      </c>
+      <c r="G17">
+        <v>0.116</v>
+      </c>
+      <c r="H17">
+        <v>11.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.46</v>
+      </c>
+      <c r="K17">
+        <v>0.46</v>
+      </c>
+      <c r="L17">
+        <v>2</v>
+      </c>
+      <c r="M17">
+        <v>0.1058412</v>
+      </c>
+      <c r="N17">
+        <v>1.8941588</v>
+      </c>
+      <c r="O17">
+        <v>0.3788317599999999</v>
+      </c>
+      <c r="P17">
+        <v>1.51532704</v>
+      </c>
+      <c r="Q17">
+        <v>1.97532704</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.201796432443821</v>
+      </c>
+      <c r="T17">
+        <v>1.191171497809921</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2</v>
+      </c>
+      <c r="W17">
+        <v>0.03656</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>18.89623322486895</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1767029037265731</v>
+      </c>
+      <c r="C18">
+        <v>13.90858827859123</v>
+      </c>
+      <c r="D18">
+        <v>16.26298827859123</v>
+      </c>
+      <c r="E18">
+        <v>-1.2696</v>
+      </c>
+      <c r="F18">
+        <v>2.4704</v>
+      </c>
+      <c r="G18">
+        <v>0.116</v>
+      </c>
+      <c r="H18">
+        <v>11.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.46</v>
+      </c>
+      <c r="K18">
+        <v>0.46</v>
+      </c>
+      <c r="L18">
+        <v>2</v>
+      </c>
+      <c r="M18">
+        <v>0.11289728</v>
+      </c>
+      <c r="N18">
+        <v>1.88710272</v>
+      </c>
+      <c r="O18">
+        <v>0.3774205439999999</v>
+      </c>
+      <c r="P18">
+        <v>1.509682176</v>
+      </c>
+      <c r="Q18">
+        <v>1.969682176</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.2033967901506822</v>
+      </c>
+      <c r="T18">
+        <v>1.2028668487948</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2</v>
+      </c>
+      <c r="W18">
+        <v>0.03656</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>17.71521864831464</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1763948398758984</v>
+      </c>
+      <c r="C19">
+        <v>13.79059980970024</v>
+      </c>
+      <c r="D19">
+        <v>16.29939980970024</v>
+      </c>
+      <c r="E19">
+        <v>-1.1152</v>
+      </c>
+      <c r="F19">
+        <v>2.6248</v>
+      </c>
+      <c r="G19">
+        <v>0.116</v>
+      </c>
+      <c r="H19">
+        <v>11.7</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.46</v>
+      </c>
+      <c r="K19">
+        <v>0.46</v>
+      </c>
+      <c r="L19">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>0.11995336</v>
+      </c>
+      <c r="N19">
+        <v>1.88004664</v>
+      </c>
+      <c r="O19">
+        <v>0.3760093279999999</v>
+      </c>
+      <c r="P19">
+        <v>1.504037312</v>
+      </c>
+      <c r="Q19">
+        <v>1.964037312</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.2050357106938534</v>
+      </c>
+      <c r="T19">
+        <v>1.214844015466061</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2</v>
+      </c>
+      <c r="W19">
+        <v>0.03656</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>16.67314696311966</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1760867760252236</v>
+      </c>
+      <c r="C20">
+        <v>13.67277475168985</v>
+      </c>
+      <c r="D20">
+        <v>16.33597475168985</v>
+      </c>
+      <c r="E20">
+        <v>-0.9608000000000003</v>
+      </c>
+      <c r="F20">
+        <v>2.7792</v>
+      </c>
+      <c r="G20">
+        <v>0.116</v>
+      </c>
+      <c r="H20">
+        <v>11.7</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.46</v>
+      </c>
+      <c r="K20">
+        <v>0.46</v>
+      </c>
+      <c r="L20">
+        <v>2</v>
+      </c>
+      <c r="M20">
+        <v>0.12700944</v>
+      </c>
+      <c r="N20">
+        <v>1.87299056</v>
+      </c>
+      <c r="O20">
+        <v>0.3745981119999999</v>
+      </c>
+      <c r="P20">
+        <v>1.498392448</v>
+      </c>
+      <c r="Q20">
+        <v>1.958392448</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.2067146049088093</v>
+      </c>
+      <c r="T20">
+        <v>1.227113308153695</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2</v>
+      </c>
+      <c r="W20">
+        <v>0.03656</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>15.74686102072413</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1757787121745489</v>
+      </c>
+      <c r="C21">
+        <v>13.55511420708872</v>
+      </c>
+      <c r="D21">
+        <v>16.37271420708872</v>
+      </c>
+      <c r="E21">
+        <v>-0.8064000000000004</v>
+      </c>
+      <c r="F21">
+        <v>2.9336</v>
+      </c>
+      <c r="G21">
+        <v>0.116</v>
+      </c>
+      <c r="H21">
+        <v>11.7</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.46</v>
+      </c>
+      <c r="K21">
+        <v>0.46</v>
+      </c>
+      <c r="L21">
+        <v>2</v>
+      </c>
+      <c r="M21">
+        <v>0.13406552</v>
+      </c>
+      <c r="N21">
+        <v>1.86593448</v>
+      </c>
+      <c r="O21">
+        <v>0.3731868959999999</v>
+      </c>
+      <c r="P21">
+        <v>1.492747584</v>
+      </c>
+      <c r="Q21">
+        <v>1.952747584</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.2084349533019122</v>
+      </c>
+      <c r="T21">
+        <v>1.239685546339789</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2</v>
+      </c>
+      <c r="W21">
+        <v>0.03656</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>14.91807886173865</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1754706483238742</v>
+      </c>
+      <c r="C22">
+        <v>13.43761928836615</v>
+      </c>
+      <c r="D22">
+        <v>16.40961928836616</v>
+      </c>
+      <c r="E22">
+        <v>-0.6520000000000001</v>
+      </c>
+      <c r="F22">
+        <v>3.088</v>
+      </c>
+      <c r="G22">
+        <v>0.116</v>
+      </c>
+      <c r="H22">
+        <v>11.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.46</v>
+      </c>
+      <c r="K22">
+        <v>0.46</v>
+      </c>
+      <c r="L22">
+        <v>2</v>
+      </c>
+      <c r="M22">
+        <v>0.1411216</v>
+      </c>
+      <c r="N22">
+        <v>1.8588784</v>
+      </c>
+      <c r="O22">
+        <v>0.3717756799999999</v>
+      </c>
+      <c r="P22">
+        <v>1.48710272</v>
+      </c>
+      <c r="Q22">
+        <v>1.94710272</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.2101983104048427</v>
+      </c>
+      <c r="T22">
+        <v>1.252572090480535</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2</v>
+      </c>
+      <c r="W22">
+        <v>0.03656</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>14.17217491865171</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1751625844731994</v>
+      </c>
+      <c r="C23">
+        <v>13.32029111804444</v>
+      </c>
+      <c r="D23">
+        <v>16.44669111804444</v>
+      </c>
+      <c r="E23">
+        <v>-0.4976000000000003</v>
+      </c>
+      <c r="F23">
+        <v>3.2424</v>
+      </c>
+      <c r="G23">
+        <v>0.116</v>
+      </c>
+      <c r="H23">
+        <v>11.7</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.46</v>
+      </c>
+      <c r="K23">
+        <v>0.46</v>
+      </c>
+      <c r="L23">
+        <v>2</v>
+      </c>
+      <c r="M23">
+        <v>0.14817768</v>
+      </c>
+      <c r="N23">
+        <v>1.85182232</v>
+      </c>
+      <c r="O23">
+        <v>0.3703644639999999</v>
+      </c>
+      <c r="P23">
+        <v>1.481457856</v>
+      </c>
+      <c r="Q23">
+        <v>1.941457856</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.2120063094597461</v>
+      </c>
+      <c r="T23">
+        <v>1.265784876245098</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2</v>
+      </c>
+      <c r="W23">
+        <v>0.03656</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>13.49730944633497</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1751361206225247</v>
+      </c>
+      <c r="C24">
+        <v>13.16908354258941</v>
+      </c>
+      <c r="D24">
+        <v>16.44988354258941</v>
+      </c>
+      <c r="E24">
+        <v>-0.3432000000000004</v>
+      </c>
+      <c r="F24">
+        <v>3.3968</v>
+      </c>
+      <c r="G24">
+        <v>0.116</v>
+      </c>
+      <c r="H24">
+        <v>11.7</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.46</v>
+      </c>
+      <c r="K24">
+        <v>0.46</v>
+      </c>
+      <c r="L24">
+        <v>2</v>
+      </c>
+      <c r="M24">
+        <v>0.16066864</v>
+      </c>
+      <c r="N24">
+        <v>1.83933136</v>
+      </c>
+      <c r="O24">
+        <v>0.3678662719999999</v>
+      </c>
+      <c r="P24">
+        <v>1.471465088</v>
+      </c>
+      <c r="Q24">
+        <v>1.931465088</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.2138606674647752</v>
+      </c>
+      <c r="T24">
+        <v>1.279336451388239</v>
+      </c>
+      <c r="U24">
+        <v>0.0473</v>
+      </c>
+      <c r="V24">
+        <v>0.2</v>
+      </c>
+      <c r="W24">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>12.4479798920312</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1748408567718499</v>
+      </c>
+      <c r="C25">
+        <v>13.05038646355882</v>
+      </c>
+      <c r="D25">
+        <v>16.48558646355882</v>
+      </c>
+      <c r="E25">
+        <v>-0.1888000000000001</v>
+      </c>
+      <c r="F25">
+        <v>3.5512</v>
+      </c>
+      <c r="G25">
+        <v>0.116</v>
+      </c>
+      <c r="H25">
+        <v>11.7</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.46</v>
+      </c>
+      <c r="K25">
+        <v>0.46</v>
+      </c>
+      <c r="L25">
+        <v>2</v>
+      </c>
+      <c r="M25">
+        <v>0.16797176</v>
+      </c>
+      <c r="N25">
+        <v>1.83202824</v>
+      </c>
+      <c r="O25">
+        <v>0.3664056479999999</v>
+      </c>
+      <c r="P25">
+        <v>1.465622592</v>
+      </c>
+      <c r="Q25">
+        <v>1.925622592</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.2157631906127921</v>
+      </c>
+      <c r="T25">
+        <v>1.293240015496137</v>
+      </c>
+      <c r="U25">
+        <v>0.0473</v>
+      </c>
+      <c r="V25">
+        <v>0.2</v>
+      </c>
+      <c r="W25">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>11.90676337498637</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1745455929211752</v>
+      </c>
+      <c r="C26">
+        <v>12.93184470127478</v>
+      </c>
+      <c r="D26">
+        <v>16.52144470127478</v>
+      </c>
+      <c r="E26">
+        <v>-0.03440000000000065</v>
+      </c>
+      <c r="F26">
+        <v>3.7056</v>
+      </c>
+      <c r="G26">
+        <v>0.116</v>
+      </c>
+      <c r="H26">
+        <v>11.7</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.46</v>
+      </c>
+      <c r="K26">
+        <v>0.46</v>
+      </c>
+      <c r="L26">
+        <v>2</v>
+      </c>
+      <c r="M26">
+        <v>0.17527488</v>
+      </c>
+      <c r="N26">
+        <v>1.82472512</v>
+      </c>
+      <c r="O26">
+        <v>0.364945024</v>
+      </c>
+      <c r="P26">
+        <v>1.459780096</v>
+      </c>
+      <c r="Q26">
+        <v>1.919780096</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.217715780159441</v>
+      </c>
+      <c r="T26">
+        <v>1.307509462870032</v>
+      </c>
+      <c r="U26">
+        <v>0.0473</v>
+      </c>
+      <c r="V26">
+        <v>0.2</v>
+      </c>
+      <c r="W26">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>11.41064823436194</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1742503290705004</v>
+      </c>
+      <c r="C27">
+        <v>12.81345927144736</v>
+      </c>
+      <c r="D27">
+        <v>16.55745927144736</v>
+      </c>
+      <c r="E27">
+        <v>0.1199999999999997</v>
+      </c>
+      <c r="F27">
+        <v>3.86</v>
+      </c>
+      <c r="G27">
+        <v>0.116</v>
+      </c>
+      <c r="H27">
+        <v>11.7</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.46</v>
+      </c>
+      <c r="K27">
+        <v>0.46</v>
+      </c>
+      <c r="L27">
+        <v>2</v>
+      </c>
+      <c r="M27">
+        <v>0.182578</v>
+      </c>
+      <c r="N27">
+        <v>1.817422</v>
+      </c>
+      <c r="O27">
+        <v>0.3634843999999999</v>
+      </c>
+      <c r="P27">
+        <v>1.4539376</v>
+      </c>
+      <c r="Q27">
+        <v>1.9139376</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.2197204387606673</v>
+      </c>
+      <c r="T27">
+        <v>1.322159428840565</v>
+      </c>
+      <c r="U27">
+        <v>0.0473</v>
+      </c>
+      <c r="V27">
+        <v>0.2</v>
+      </c>
+      <c r="W27">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>10.95422230498746</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1739550652198257</v>
+      </c>
+      <c r="C28">
+        <v>12.69523119866241</v>
+      </c>
+      <c r="D28">
+        <v>16.59363119866241</v>
+      </c>
+      <c r="E28">
+        <v>0.2744</v>
+      </c>
+      <c r="F28">
+        <v>4.0144</v>
+      </c>
+      <c r="G28">
+        <v>0.116</v>
+      </c>
+      <c r="H28">
+        <v>11.7</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.46</v>
+      </c>
+      <c r="K28">
+        <v>0.46</v>
+      </c>
+      <c r="L28">
+        <v>2</v>
+      </c>
+      <c r="M28">
+        <v>0.18988112</v>
+      </c>
+      <c r="N28">
+        <v>1.81011888</v>
+      </c>
+      <c r="O28">
+        <v>0.362023776</v>
+      </c>
+      <c r="P28">
+        <v>1.448095104</v>
+      </c>
+      <c r="Q28">
+        <v>1.908095104</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.2217792773240888</v>
+      </c>
+      <c r="T28">
+        <v>1.337205339837328</v>
+      </c>
+      <c r="U28">
+        <v>0.0473</v>
+      </c>
+      <c r="V28">
+        <v>0.2</v>
+      </c>
+      <c r="W28">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>10.53290606248794</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.174480601369151</v>
+      </c>
+      <c r="C29">
+        <v>12.47655853952418</v>
+      </c>
+      <c r="D29">
+        <v>16.52935853952419</v>
+      </c>
+      <c r="E29">
+        <v>0.4287999999999998</v>
+      </c>
+      <c r="F29">
+        <v>4.1688</v>
+      </c>
+      <c r="G29">
+        <v>0.116</v>
+      </c>
+      <c r="H29">
+        <v>11.7</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.46</v>
+      </c>
+      <c r="K29">
+        <v>0.46</v>
+      </c>
+      <c r="L29">
+        <v>2</v>
+      </c>
+      <c r="M29">
+        <v>0.21302568</v>
+      </c>
+      <c r="N29">
+        <v>1.78697432</v>
+      </c>
+      <c r="O29">
+        <v>0.3573948639999999</v>
+      </c>
+      <c r="P29">
+        <v>1.429579456</v>
+      </c>
+      <c r="Q29">
+        <v>1.889579456</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.2238945224234945</v>
+      </c>
+      <c r="T29">
+        <v>1.352663467573729</v>
+      </c>
+      <c r="U29">
+        <v>0.0511</v>
+      </c>
+      <c r="V29">
+        <v>0.2</v>
+      </c>
+      <c r="W29">
+        <v>0.04088</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>9.388539447450656</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1742157375184762</v>
+      </c>
+      <c r="C30">
+        <v>12.354488825739</v>
+      </c>
+      <c r="D30">
+        <v>16.561688825739</v>
+      </c>
+      <c r="E30">
+        <v>0.5831999999999997</v>
+      </c>
+      <c r="F30">
+        <v>4.3232</v>
+      </c>
+      <c r="G30">
+        <v>0.116</v>
+      </c>
+      <c r="H30">
+        <v>11.7</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.46</v>
+      </c>
+      <c r="K30">
+        <v>0.46</v>
+      </c>
+      <c r="L30">
+        <v>2</v>
+      </c>
+      <c r="M30">
+        <v>0.22091552</v>
+      </c>
+      <c r="N30">
+        <v>1.77908448</v>
+      </c>
+      <c r="O30">
+        <v>0.3558168959999999</v>
+      </c>
+      <c r="P30">
+        <v>1.423267584</v>
+      </c>
+      <c r="Q30">
+        <v>1.883267584</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.226068524331217</v>
+      </c>
+      <c r="T30">
+        <v>1.368550987747251</v>
+      </c>
+      <c r="U30">
+        <v>0.0511</v>
+      </c>
+      <c r="V30">
+        <v>0.2</v>
+      </c>
+      <c r="W30">
+        <v>0.04088</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>9.053234467184561</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1739508736678015</v>
+      </c>
+      <c r="C31">
+        <v>12.23254583143209</v>
+      </c>
+      <c r="D31">
+        <v>16.59414583143209</v>
+      </c>
+      <c r="E31">
+        <v>0.7375999999999996</v>
+      </c>
+      <c r="F31">
+        <v>4.4776</v>
+      </c>
+      <c r="G31">
+        <v>0.116</v>
+      </c>
+      <c r="H31">
+        <v>11.7</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.46</v>
+      </c>
+      <c r="K31">
+        <v>0.46</v>
+      </c>
+      <c r="L31">
+        <v>2</v>
+      </c>
+      <c r="M31">
+        <v>0.22880536</v>
+      </c>
+      <c r="N31">
+        <v>1.77119464</v>
+      </c>
+      <c r="O31">
+        <v>0.354238928</v>
+      </c>
+      <c r="P31">
+        <v>1.416955712</v>
+      </c>
+      <c r="Q31">
+        <v>1.876955712</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.2283037657292979</v>
+      </c>
+      <c r="T31">
+        <v>1.38488604370031</v>
+      </c>
+      <c r="U31">
+        <v>0.0511</v>
+      </c>
+      <c r="V31">
+        <v>0.2</v>
+      </c>
+      <c r="W31">
+        <v>0.04088</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>8.741053968316127</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1736860098171268</v>
+      </c>
+      <c r="C32">
+        <v>12.11073030308731</v>
+      </c>
+      <c r="D32">
+        <v>16.62673030308731</v>
+      </c>
+      <c r="E32">
+        <v>0.8919999999999995</v>
+      </c>
+      <c r="F32">
+        <v>4.632</v>
+      </c>
+      <c r="G32">
+        <v>0.116</v>
+      </c>
+      <c r="H32">
+        <v>11.7</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.46</v>
+      </c>
+      <c r="K32">
+        <v>0.46</v>
+      </c>
+      <c r="L32">
+        <v>2</v>
+      </c>
+      <c r="M32">
+        <v>0.2366952</v>
+      </c>
+      <c r="N32">
+        <v>1.7633048</v>
+      </c>
+      <c r="O32">
+        <v>0.3526609599999999</v>
+      </c>
+      <c r="P32">
+        <v>1.41064384</v>
+      </c>
+      <c r="Q32">
+        <v>1.87064384</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.230602871167324</v>
+      </c>
+      <c r="T32">
+        <v>1.401687815537742</v>
+      </c>
+      <c r="U32">
+        <v>0.0511</v>
+      </c>
+      <c r="V32">
+        <v>0.2</v>
+      </c>
+      <c r="W32">
+        <v>0.04088</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>8.44968550270559</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1734211459664521</v>
+      </c>
+      <c r="C33">
+        <v>11.98904299306324</v>
+      </c>
+      <c r="D33">
+        <v>16.65944299306324</v>
+      </c>
+      <c r="E33">
+        <v>1.046399999999999</v>
+      </c>
+      <c r="F33">
+        <v>4.7864</v>
+      </c>
+      <c r="G33">
+        <v>0.116</v>
+      </c>
+      <c r="H33">
+        <v>11.7</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.46</v>
+      </c>
+      <c r="K33">
+        <v>0.46</v>
+      </c>
+      <c r="L33">
+        <v>2</v>
+      </c>
+      <c r="M33">
+        <v>0.24458504</v>
+      </c>
+      <c r="N33">
+        <v>1.75541496</v>
+      </c>
+      <c r="O33">
+        <v>0.3510829919999999</v>
+      </c>
+      <c r="P33">
+        <v>1.404331968</v>
+      </c>
+      <c r="Q33">
+        <v>1.864331968</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.2329686173426841</v>
+      </c>
+      <c r="T33">
+        <v>1.418976595254519</v>
+      </c>
+      <c r="U33">
+        <v>0.0511</v>
+      </c>
+      <c r="V33">
+        <v>0.2</v>
+      </c>
+      <c r="W33">
+        <v>0.04088</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>8.177115002618311</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1731562821157773</v>
+      </c>
+      <c r="C34">
+        <v>11.86748465965116</v>
+      </c>
+      <c r="D34">
+        <v>16.69228465965116</v>
+      </c>
+      <c r="E34">
+        <v>1.2008</v>
+      </c>
+      <c r="F34">
+        <v>4.9408</v>
+      </c>
+      <c r="G34">
+        <v>0.116</v>
+      </c>
+      <c r="H34">
+        <v>11.7</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.46</v>
+      </c>
+      <c r="K34">
+        <v>0.46</v>
+      </c>
+      <c r="L34">
+        <v>2</v>
+      </c>
+      <c r="M34">
+        <v>0.25247488</v>
+      </c>
+      <c r="N34">
+        <v>1.74752512</v>
+      </c>
+      <c r="O34">
+        <v>0.3495050239999999</v>
+      </c>
+      <c r="P34">
+        <v>1.398020096</v>
+      </c>
+      <c r="Q34">
+        <v>1.858020096</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.2354039442879078</v>
+      </c>
+      <c r="T34">
+        <v>1.436773868492379</v>
+      </c>
+      <c r="U34">
+        <v>0.0511</v>
+      </c>
+      <c r="V34">
+        <v>0.2</v>
+      </c>
+      <c r="W34">
+        <v>0.04088</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>7.921580158786489</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1733930182651025</v>
+      </c>
+      <c r="C35">
+        <v>11.68372453945545</v>
+      </c>
+      <c r="D35">
+        <v>16.66292453945545</v>
+      </c>
+      <c r="E35">
+        <v>1.3552</v>
+      </c>
+      <c r="F35">
+        <v>5.0952</v>
+      </c>
+      <c r="G35">
+        <v>0.116</v>
+      </c>
+      <c r="H35">
+        <v>11.7</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.46</v>
+      </c>
+      <c r="K35">
+        <v>0.46</v>
+      </c>
+      <c r="L35">
+        <v>2</v>
+      </c>
+      <c r="M35">
+        <v>0.2700456000000001</v>
+      </c>
+      <c r="N35">
+        <v>1.7299544</v>
+      </c>
+      <c r="O35">
+        <v>0.3459908799999999</v>
+      </c>
+      <c r="P35">
+        <v>1.38396352</v>
+      </c>
+      <c r="Q35">
+        <v>1.84396352</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.2379119675598546</v>
+      </c>
+      <c r="T35">
+        <v>1.455102403617935</v>
+      </c>
+      <c r="U35">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0.2</v>
+      </c>
+      <c r="W35">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>7.406156589850009</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1731433544144278</v>
+      </c>
+      <c r="C36">
+        <v>11.56029093836782</v>
+      </c>
+      <c r="D36">
+        <v>16.69389093836782</v>
+      </c>
+      <c r="E36">
+        <v>1.5096</v>
+      </c>
+      <c r="F36">
+        <v>5.2496</v>
+      </c>
+      <c r="G36">
+        <v>0.116</v>
+      </c>
+      <c r="H36">
+        <v>11.7</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.46</v>
+      </c>
+      <c r="K36">
+        <v>0.46</v>
+      </c>
+      <c r="L36">
+        <v>2</v>
+      </c>
+      <c r="M36">
+        <v>0.2782288000000001</v>
+      </c>
+      <c r="N36">
+        <v>1.7217712</v>
+      </c>
+      <c r="O36">
+        <v>0.3443542399999999</v>
+      </c>
+      <c r="P36">
+        <v>1.37741696</v>
+      </c>
+      <c r="Q36">
+        <v>1.83741696</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.2404959915370118</v>
+      </c>
+      <c r="T36">
+        <v>1.473986348898812</v>
+      </c>
+      <c r="U36">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0.2</v>
+      </c>
+      <c r="W36">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>7.188328454854421</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.172893690563753</v>
+      </c>
+      <c r="C37">
+        <v>11.43697264755858</v>
+      </c>
+      <c r="D37">
+        <v>16.72497264755858</v>
+      </c>
+      <c r="E37">
+        <v>1.664</v>
+      </c>
+      <c r="F37">
+        <v>5.404</v>
+      </c>
+      <c r="G37">
+        <v>0.116</v>
+      </c>
+      <c r="H37">
+        <v>11.7</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.46</v>
+      </c>
+      <c r="K37">
+        <v>0.46</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="M37">
+        <v>0.286412</v>
+      </c>
+      <c r="N37">
+        <v>1.713588</v>
+      </c>
+      <c r="O37">
+        <v>0.3427176</v>
+      </c>
+      <c r="P37">
+        <v>1.3708704</v>
+      </c>
+      <c r="Q37">
+        <v>1.8308704</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.2431595239442355</v>
+      </c>
+      <c r="T37">
+        <v>1.493451338649869</v>
+      </c>
+      <c r="U37">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V37">
+        <v>0.2</v>
+      </c>
+      <c r="W37">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>6.982947641858582</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1726440267130784</v>
+      </c>
+      <c r="C38">
+        <v>11.31377031230434</v>
+      </c>
+      <c r="D38">
+        <v>16.75617031230434</v>
+      </c>
+      <c r="E38">
+        <v>1.8184</v>
+      </c>
+      <c r="F38">
+        <v>5.5584</v>
+      </c>
+      <c r="G38">
+        <v>0.116</v>
+      </c>
+      <c r="H38">
+        <v>11.7</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.46</v>
+      </c>
+      <c r="K38">
+        <v>0.46</v>
+      </c>
+      <c r="L38">
+        <v>2</v>
+      </c>
+      <c r="M38">
+        <v>0.2945952</v>
+      </c>
+      <c r="N38">
+        <v>1.7054048</v>
+      </c>
+      <c r="O38">
+        <v>0.3410809599999999</v>
+      </c>
+      <c r="P38">
+        <v>1.36432384</v>
+      </c>
+      <c r="Q38">
+        <v>1.82432384</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.2459062917391849</v>
+      </c>
+      <c r="T38">
+        <v>1.513524609330647</v>
+      </c>
+      <c r="U38">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V38">
+        <v>0.2</v>
+      </c>
+      <c r="W38">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>6.788976874029176</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1723943628624036</v>
+      </c>
+      <c r="C39">
+        <v>11.19068458270541</v>
+      </c>
+      <c r="D39">
+        <v>16.78748458270541</v>
+      </c>
+      <c r="E39">
+        <v>1.972799999999999</v>
+      </c>
+      <c r="F39">
+        <v>5.7128</v>
+      </c>
+      <c r="G39">
+        <v>0.116</v>
+      </c>
+      <c r="H39">
+        <v>11.7</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.46</v>
+      </c>
+      <c r="K39">
+        <v>0.46</v>
+      </c>
+      <c r="L39">
+        <v>2</v>
+      </c>
+      <c r="M39">
+        <v>0.3027784</v>
+      </c>
+      <c r="N39">
+        <v>1.6972216</v>
+      </c>
+      <c r="O39">
+        <v>0.3394443199999999</v>
+      </c>
+      <c r="P39">
+        <v>1.35777728</v>
+      </c>
+      <c r="Q39">
+        <v>1.81777728</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.2487402585117518</v>
+      </c>
+      <c r="T39">
+        <v>1.534235126699703</v>
+      </c>
+      <c r="U39">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V39">
+        <v>0.2</v>
+      </c>
+      <c r="W39">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>6.605491012568928</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1721446990117289</v>
+      </c>
+      <c r="C40">
+        <v>11.06771611373082</v>
+      </c>
+      <c r="D40">
+        <v>16.81891611373082</v>
+      </c>
+      <c r="E40">
+        <v>2.127199999999999</v>
+      </c>
+      <c r="F40">
+        <v>5.8672</v>
+      </c>
+      <c r="G40">
+        <v>0.116</v>
+      </c>
+      <c r="H40">
+        <v>11.7</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.46</v>
+      </c>
+      <c r="K40">
+        <v>0.46</v>
+      </c>
+      <c r="L40">
+        <v>2</v>
+      </c>
+      <c r="M40">
+        <v>0.3109616</v>
+      </c>
+      <c r="N40">
+        <v>1.6890384</v>
+      </c>
+      <c r="O40">
+        <v>0.3378076799999999</v>
+      </c>
+      <c r="P40">
+        <v>1.35123072</v>
+      </c>
+      <c r="Q40">
+        <v>1.81123072</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.2516656435673046</v>
+      </c>
+      <c r="T40">
+        <v>1.555613725274213</v>
+      </c>
+      <c r="U40">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V40">
+        <v>0.2</v>
+      </c>
+      <c r="W40">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>6.431662301711851</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1718950351610541</v>
+      </c>
+      <c r="C41">
+        <v>10.94486556526407</v>
+      </c>
+      <c r="D41">
+        <v>16.85046556526407</v>
+      </c>
+      <c r="E41">
+        <v>2.2816</v>
+      </c>
+      <c r="F41">
+        <v>6.0216</v>
+      </c>
+      <c r="G41">
+        <v>0.116</v>
+      </c>
+      <c r="H41">
+        <v>11.7</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.46</v>
+      </c>
+      <c r="K41">
+        <v>0.46</v>
+      </c>
+      <c r="L41">
+        <v>2</v>
+      </c>
+      <c r="M41">
+        <v>0.3191448000000001</v>
+      </c>
+      <c r="N41">
+        <v>1.6808552</v>
+      </c>
+      <c r="O41">
+        <v>0.3361710399999999</v>
+      </c>
+      <c r="P41">
+        <v>1.34468416</v>
+      </c>
+      <c r="Q41">
+        <v>1.80468416</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.254686942886974</v>
+      </c>
+      <c r="T41">
+        <v>1.577693261506904</v>
+      </c>
+      <c r="U41">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V41">
+        <v>0.2</v>
+      </c>
+      <c r="W41">
+        <v>0.04240000000000001</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>6.266747883719238</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1722853713103794</v>
+      </c>
+      <c r="C42">
+        <v>10.74119165773011</v>
+      </c>
+      <c r="D42">
+        <v>16.80119165773012</v>
+      </c>
+      <c r="E42">
+        <v>2.436</v>
+      </c>
+      <c r="F42">
+        <v>6.176</v>
+      </c>
+      <c r="G42">
+        <v>0.116</v>
+      </c>
+      <c r="H42">
+        <v>11.7</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.46</v>
+      </c>
+      <c r="K42">
+        <v>0.46</v>
+      </c>
+      <c r="L42">
+        <v>2</v>
+      </c>
+      <c r="M42">
+        <v>0.33968</v>
+      </c>
+      <c r="N42">
+        <v>1.66032</v>
+      </c>
+      <c r="O42">
+        <v>0.3320639999999999</v>
+      </c>
+      <c r="P42">
+        <v>1.328256</v>
+      </c>
+      <c r="Q42">
+        <v>1.788256</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.2578089521839657</v>
+      </c>
+      <c r="T42">
+        <v>1.600508782280684</v>
+      </c>
+      <c r="U42">
+        <v>0.055</v>
+      </c>
+      <c r="V42">
+        <v>0.2</v>
+      </c>
+      <c r="W42">
+        <v>0.044</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>5.887894488930758</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1720517074597046</v>
+      </c>
+      <c r="C43">
+        <v>10.61625342759041</v>
+      </c>
+      <c r="D43">
+        <v>16.83065342759041</v>
+      </c>
+      <c r="E43">
+        <v>2.5904</v>
+      </c>
+      <c r="F43">
+        <v>6.3304</v>
+      </c>
+      <c r="G43">
+        <v>0.116</v>
+      </c>
+      <c r="H43">
+        <v>11.7</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.46</v>
+      </c>
+      <c r="K43">
+        <v>0.46</v>
+      </c>
+      <c r="L43">
+        <v>2</v>
+      </c>
+      <c r="M43">
+        <v>0.348172</v>
+      </c>
+      <c r="N43">
+        <v>1.651828</v>
+      </c>
+      <c r="O43">
+        <v>0.3303655999999999</v>
+      </c>
+      <c r="P43">
+        <v>1.3214624</v>
+      </c>
+      <c r="Q43">
+        <v>1.7814624</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.2610367923045842</v>
+      </c>
+      <c r="T43">
+        <v>1.624097710538321</v>
+      </c>
+      <c r="U43">
+        <v>0.055</v>
+      </c>
+      <c r="V43">
+        <v>0.2</v>
+      </c>
+      <c r="W43">
+        <v>0.044</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>5.744287306273911</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1718180436090299</v>
+      </c>
+      <c r="C44">
+        <v>10.49141870446985</v>
+      </c>
+      <c r="D44">
+        <v>16.86021870446985</v>
+      </c>
+      <c r="E44">
+        <v>2.7448</v>
+      </c>
+      <c r="F44">
+        <v>6.4848</v>
+      </c>
+      <c r="G44">
+        <v>0.116</v>
+      </c>
+      <c r="H44">
+        <v>11.7</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.46</v>
+      </c>
+      <c r="K44">
+        <v>0.46</v>
+      </c>
+      <c r="L44">
+        <v>2</v>
+      </c>
+      <c r="M44">
+        <v>0.356664</v>
+      </c>
+      <c r="N44">
+        <v>1.643336</v>
+      </c>
+      <c r="O44">
+        <v>0.3286671999999999</v>
+      </c>
+      <c r="P44">
+        <v>1.3146688</v>
+      </c>
+      <c r="Q44">
+        <v>1.7746688</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.2643759372569481</v>
+      </c>
+      <c r="T44">
+        <v>1.648500050115187</v>
+      </c>
+      <c r="U44">
+        <v>0.055</v>
+      </c>
+      <c r="V44">
+        <v>0.2</v>
+      </c>
+      <c r="W44">
+        <v>0.044</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>5.607518560886438</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1715843797583552</v>
+      </c>
+      <c r="C45">
+        <v>10.36668803479977</v>
+      </c>
+      <c r="D45">
+        <v>16.88988803479977</v>
+      </c>
+      <c r="E45">
+        <v>2.8992</v>
+      </c>
+      <c r="F45">
+        <v>6.6392</v>
+      </c>
+      <c r="G45">
+        <v>0.116</v>
+      </c>
+      <c r="H45">
+        <v>11.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.46</v>
+      </c>
+      <c r="K45">
+        <v>0.46</v>
+      </c>
+      <c r="L45">
+        <v>2</v>
+      </c>
+      <c r="M45">
+        <v>0.365156</v>
+      </c>
+      <c r="N45">
+        <v>1.634844</v>
+      </c>
+      <c r="O45">
+        <v>0.3269687999999999</v>
+      </c>
+      <c r="P45">
+        <v>1.3078752</v>
+      </c>
+      <c r="Q45">
+        <v>1.7678752</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.2678322451900969</v>
+      </c>
+      <c r="T45">
+        <v>1.673758612133347</v>
+      </c>
+      <c r="U45">
+        <v>0.055</v>
+      </c>
+      <c r="V45">
+        <v>0.2</v>
+      </c>
+      <c r="W45">
+        <v>0.044</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>5.477111152493729</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1713507159076804</v>
+      </c>
+      <c r="C46">
+        <v>10.24206196886458</v>
+      </c>
+      <c r="D46">
+        <v>16.91966196886458</v>
+      </c>
+      <c r="E46">
+        <v>3.053599999999999</v>
+      </c>
+      <c r="F46">
+        <v>6.7936</v>
+      </c>
+      <c r="G46">
+        <v>0.116</v>
+      </c>
+      <c r="H46">
+        <v>11.7</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.46</v>
+      </c>
+      <c r="K46">
+        <v>0.46</v>
+      </c>
+      <c r="L46">
+        <v>2</v>
+      </c>
+      <c r="M46">
+        <v>0.373648</v>
+      </c>
+      <c r="N46">
+        <v>1.626352</v>
+      </c>
+      <c r="O46">
+        <v>0.3252703999999999</v>
+      </c>
+      <c r="P46">
+        <v>1.3010816</v>
+      </c>
+      <c r="Q46">
+        <v>1.7610816</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.2714119926922864</v>
+      </c>
+      <c r="T46">
+        <v>1.699919265652155</v>
+      </c>
+      <c r="U46">
+        <v>0.055</v>
+      </c>
+      <c r="V46">
+        <v>0.2</v>
+      </c>
+      <c r="W46">
+        <v>0.044</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>5.352631353573417</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1711170520570057</v>
+      </c>
+      <c r="C47">
+        <v>10.11754106083569</v>
+      </c>
+      <c r="D47">
+        <v>16.9495410608357</v>
+      </c>
+      <c r="E47">
+        <v>3.207999999999999</v>
+      </c>
+      <c r="F47">
+        <v>6.948</v>
+      </c>
+      <c r="G47">
+        <v>0.116</v>
+      </c>
+      <c r="H47">
+        <v>11.7</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.46</v>
+      </c>
+      <c r="K47">
+        <v>0.46</v>
+      </c>
+      <c r="L47">
+        <v>2</v>
+      </c>
+      <c r="M47">
+        <v>0.38214</v>
+      </c>
+      <c r="N47">
+        <v>1.61786</v>
+      </c>
+      <c r="O47">
+        <v>0.323572</v>
+      </c>
+      <c r="P47">
+        <v>1.294288</v>
+      </c>
+      <c r="Q47">
+        <v>1.754288</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.2751219128309195</v>
+      </c>
+      <c r="T47">
+        <v>1.727031215662556</v>
+      </c>
+      <c r="U47">
+        <v>0.055</v>
+      </c>
+      <c r="V47">
+        <v>0.2</v>
+      </c>
+      <c r="W47">
+        <v>0.044</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>5.233683990160674</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.170883388206331</v>
+      </c>
+      <c r="C48">
+        <v>9.993125868806079</v>
+      </c>
+      <c r="D48">
+        <v>16.97952586880608</v>
+      </c>
+      <c r="E48">
+        <v>3.3624</v>
+      </c>
+      <c r="F48">
+        <v>7.1024</v>
+      </c>
+      <c r="G48">
+        <v>0.116</v>
+      </c>
+      <c r="H48">
+        <v>11.7</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.46</v>
+      </c>
+      <c r="K48">
+        <v>0.46</v>
+      </c>
+      <c r="L48">
+        <v>2</v>
+      </c>
+      <c r="M48">
+        <v>0.390632</v>
+      </c>
+      <c r="N48">
+        <v>1.609368</v>
+      </c>
+      <c r="O48">
+        <v>0.3218735999999999</v>
+      </c>
+      <c r="P48">
+        <v>1.2874944</v>
+      </c>
+      <c r="Q48">
+        <v>1.7474944</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.2789692374191314</v>
+      </c>
+      <c r="T48">
+        <v>1.755147311969639</v>
+      </c>
+      <c r="U48">
+        <v>0.055</v>
+      </c>
+      <c r="V48">
+        <v>0.2</v>
+      </c>
+      <c r="W48">
+        <v>0.044</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>5.119908251244137</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1706497243556563</v>
+      </c>
+      <c r="C49">
+        <v>9.868816954824842</v>
+      </c>
+      <c r="D49">
+        <v>17.00961695482484</v>
+      </c>
+      <c r="E49">
+        <v>3.5168</v>
+      </c>
+      <c r="F49">
+        <v>7.2568</v>
+      </c>
+      <c r="G49">
+        <v>0.116</v>
+      </c>
+      <c r="H49">
+        <v>11.7</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.46</v>
+      </c>
+      <c r="K49">
+        <v>0.46</v>
+      </c>
+      <c r="L49">
+        <v>2</v>
+      </c>
+      <c r="M49">
+        <v>0.399124</v>
+      </c>
+      <c r="N49">
+        <v>1.600876</v>
+      </c>
+      <c r="O49">
+        <v>0.3201751999999999</v>
+      </c>
+      <c r="P49">
+        <v>1.2807008</v>
+      </c>
+      <c r="Q49">
+        <v>1.7407008</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.2829617440672759</v>
+      </c>
+      <c r="T49">
+        <v>1.784324393043027</v>
+      </c>
+      <c r="U49">
+        <v>0.055</v>
+      </c>
+      <c r="V49">
+        <v>0.2</v>
+      </c>
+      <c r="W49">
+        <v>0.044</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>5.01097403313256</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1704160605049815</v>
+      </c>
+      <c r="C50">
+        <v>9.744614884932444</v>
+      </c>
+      <c r="D50">
+        <v>17.03981488493244</v>
+      </c>
+      <c r="E50">
+        <v>3.671199999999999</v>
+      </c>
+      <c r="F50">
+        <v>7.411199999999999</v>
+      </c>
+      <c r="G50">
+        <v>0.116</v>
+      </c>
+      <c r="H50">
+        <v>11.7</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.46</v>
+      </c>
+      <c r="K50">
+        <v>0.46</v>
+      </c>
+      <c r="L50">
+        <v>2</v>
+      </c>
+      <c r="M50">
+        <v>0.407616</v>
+      </c>
+      <c r="N50">
+        <v>1.592384</v>
+      </c>
+      <c r="O50">
+        <v>0.3184767999999999</v>
+      </c>
+      <c r="P50">
+        <v>1.2739072</v>
+      </c>
+      <c r="Q50">
+        <v>1.7339072</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.2871078086634259</v>
+      </c>
+      <c r="T50">
+        <v>1.814623669542314</v>
+      </c>
+      <c r="U50">
+        <v>0.055</v>
+      </c>
+      <c r="V50">
+        <v>0.2</v>
+      </c>
+      <c r="W50">
+        <v>0.044</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>4.906578740775632</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1701823966543067</v>
+      </c>
+      <c r="C51">
+        <v>9.620520229196142</v>
+      </c>
+      <c r="D51">
+        <v>17.07012022919614</v>
+      </c>
+      <c r="E51">
+        <v>3.8256</v>
+      </c>
+      <c r="F51">
+        <v>7.5656</v>
+      </c>
+      <c r="G51">
+        <v>0.116</v>
+      </c>
+      <c r="H51">
+        <v>11.7</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.46</v>
+      </c>
+      <c r="K51">
+        <v>0.46</v>
+      </c>
+      <c r="L51">
+        <v>2</v>
+      </c>
+      <c r="M51">
+        <v>0.416108</v>
+      </c>
+      <c r="N51">
+        <v>1.583892</v>
+      </c>
+      <c r="O51">
+        <v>0.3167784</v>
+      </c>
+      <c r="P51">
+        <v>1.2671136</v>
+      </c>
+      <c r="Q51">
+        <v>1.7271136</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.2914164640280524</v>
+      </c>
+      <c r="T51">
+        <v>1.846111152963142</v>
+      </c>
+      <c r="U51">
+        <v>0.055</v>
+      </c>
+      <c r="V51">
+        <v>0.2</v>
+      </c>
+      <c r="W51">
+        <v>0.044</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>4.806444480759803</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.169948732803632</v>
+      </c>
+      <c r="C52">
+        <v>9.496533561745888</v>
+      </c>
+      <c r="D52">
+        <v>17.10053356174589</v>
+      </c>
+      <c r="E52">
+        <v>3.98</v>
+      </c>
+      <c r="F52">
+        <v>7.72</v>
+      </c>
+      <c r="G52">
+        <v>0.116</v>
+      </c>
+      <c r="H52">
+        <v>11.7</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.46</v>
+      </c>
+      <c r="K52">
+        <v>0.46</v>
+      </c>
+      <c r="L52">
+        <v>2</v>
+      </c>
+      <c r="M52">
+        <v>0.4246</v>
+      </c>
+      <c r="N52">
+        <v>1.5754</v>
+      </c>
+      <c r="O52">
+        <v>0.31508</v>
+      </c>
+      <c r="P52">
+        <v>1.26032</v>
+      </c>
+      <c r="Q52">
+        <v>1.72032</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.295897465607264</v>
+      </c>
+      <c r="T52">
+        <v>1.878858135720803</v>
+      </c>
+      <c r="U52">
+        <v>0.055</v>
+      </c>
+      <c r="V52">
+        <v>0.2</v>
+      </c>
+      <c r="W52">
+        <v>0.044</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>4.710315591144607</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1697150689529573</v>
+      </c>
+      <c r="C53">
+        <v>9.372655460810583</v>
+      </c>
+      <c r="D53">
+        <v>17.13105546081058</v>
+      </c>
+      <c r="E53">
+        <v>4.134399999999999</v>
+      </c>
+      <c r="F53">
+        <v>7.8744</v>
+      </c>
+      <c r="G53">
+        <v>0.116</v>
+      </c>
+      <c r="H53">
+        <v>11.7</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.46</v>
+      </c>
+      <c r="K53">
+        <v>0.46</v>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+      <c r="M53">
+        <v>0.433092</v>
+      </c>
+      <c r="N53">
+        <v>1.566908</v>
+      </c>
+      <c r="O53">
+        <v>0.3133815999999999</v>
+      </c>
+      <c r="P53">
+        <v>1.2535264</v>
+      </c>
+      <c r="Q53">
+        <v>1.7135264</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.3005613652101169</v>
+      </c>
+      <c r="T53">
+        <v>1.912941730019593</v>
+      </c>
+      <c r="U53">
+        <v>0.055</v>
+      </c>
+      <c r="V53">
+        <v>0.2</v>
+      </c>
+      <c r="W53">
+        <v>0.044</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>4.617956461906477</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1694814051022825</v>
+      </c>
+      <c r="C54">
+        <v>9.248886508754723</v>
+      </c>
+      <c r="D54">
+        <v>17.16168650875472</v>
+      </c>
+      <c r="E54">
+        <v>4.2888</v>
+      </c>
+      <c r="F54">
+        <v>8.0288</v>
+      </c>
+      <c r="G54">
+        <v>0.116</v>
+      </c>
+      <c r="H54">
+        <v>11.7</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.46</v>
+      </c>
+      <c r="K54">
+        <v>0.46</v>
+      </c>
+      <c r="L54">
+        <v>2</v>
+      </c>
+      <c r="M54">
+        <v>0.441584</v>
+      </c>
+      <c r="N54">
+        <v>1.558416</v>
+      </c>
+      <c r="O54">
+        <v>0.3116831999999999</v>
+      </c>
+      <c r="P54">
+        <v>1.2467328</v>
+      </c>
+      <c r="Q54">
+        <v>1.7067328</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.3054195939630886</v>
+      </c>
+      <c r="T54">
+        <v>1.948445474080833</v>
+      </c>
+      <c r="U54">
+        <v>0.055</v>
+      </c>
+      <c r="V54">
+        <v>0.2</v>
+      </c>
+      <c r="W54">
+        <v>0.044</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>4.529149606869813</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1708589412516078</v>
+      </c>
+      <c r="C55">
+        <v>8.915469144802405</v>
+      </c>
+      <c r="D55">
+        <v>16.9826691448024</v>
+      </c>
+      <c r="E55">
+        <v>4.443199999999999</v>
+      </c>
+      <c r="F55">
+        <v>8.183199999999999</v>
+      </c>
+      <c r="G55">
+        <v>0.116</v>
+      </c>
+      <c r="H55">
+        <v>11.7</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.46</v>
+      </c>
+      <c r="K55">
+        <v>0.46</v>
+      </c>
+      <c r="L55">
+        <v>2</v>
+      </c>
+      <c r="M55">
+        <v>0.48117216</v>
+      </c>
+      <c r="N55">
+        <v>1.51882784</v>
+      </c>
+      <c r="O55">
+        <v>0.3037655679999999</v>
+      </c>
+      <c r="P55">
+        <v>1.215062272</v>
+      </c>
+      <c r="Q55">
+        <v>1.675062272</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.3104845558544847</v>
+      </c>
+      <c r="T55">
+        <v>1.9854600157617</v>
+      </c>
+      <c r="U55">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.2</v>
+      </c>
+      <c r="W55">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>4.156516453487251</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1706556774009331</v>
+      </c>
+      <c r="C56">
+        <v>8.78724900139372</v>
+      </c>
+      <c r="D56">
+        <v>17.00884900139372</v>
+      </c>
+      <c r="E56">
+        <v>4.5976</v>
+      </c>
+      <c r="F56">
+        <v>8.3376</v>
+      </c>
+      <c r="G56">
+        <v>0.116</v>
+      </c>
+      <c r="H56">
+        <v>11.7</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.46</v>
+      </c>
+      <c r="K56">
+        <v>0.46</v>
+      </c>
+      <c r="L56">
+        <v>2</v>
+      </c>
+      <c r="M56">
+        <v>0.4902508800000001</v>
+      </c>
+      <c r="N56">
+        <v>1.50974912</v>
+      </c>
+      <c r="O56">
+        <v>0.3019498239999999</v>
+      </c>
+      <c r="P56">
+        <v>1.207799296</v>
+      </c>
+      <c r="Q56">
+        <v>1.667799296</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.3157697334802893</v>
+      </c>
+      <c r="T56">
+        <v>2.024083885341735</v>
+      </c>
+      <c r="U56">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.2</v>
+      </c>
+      <c r="W56">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>4.079543926570819</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1704524135502583</v>
+      </c>
+      <c r="C57">
+        <v>8.659109698408965</v>
+      </c>
+      <c r="D57">
+        <v>17.03510969840897</v>
+      </c>
+      <c r="E57">
+        <v>4.752000000000001</v>
+      </c>
+      <c r="F57">
+        <v>8.492000000000001</v>
+      </c>
+      <c r="G57">
+        <v>0.116</v>
+      </c>
+      <c r="H57">
+        <v>11.7</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.46</v>
+      </c>
+      <c r="K57">
+        <v>0.46</v>
+      </c>
+      <c r="L57">
+        <v>2</v>
+      </c>
+      <c r="M57">
+        <v>0.4993296000000001</v>
+      </c>
+      <c r="N57">
+        <v>1.5006704</v>
+      </c>
+      <c r="O57">
+        <v>0.3001340799999999</v>
+      </c>
+      <c r="P57">
+        <v>1.20053632</v>
+      </c>
+      <c r="Q57">
+        <v>1.66053632</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.3212898078894629</v>
+      </c>
+      <c r="T57">
+        <v>2.064424371347549</v>
+      </c>
+      <c r="U57">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V57">
+        <v>0.2</v>
+      </c>
+      <c r="W57">
+        <v>0.04704000000000001</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>4.005370400633169</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1721307496995836</v>
+      </c>
+      <c r="C58">
+        <v>8.290275740158666</v>
+      </c>
+      <c r="D58">
+        <v>16.82067574015867</v>
+      </c>
+      <c r="E58">
+        <v>4.9064</v>
+      </c>
+      <c r="F58">
+        <v>8.6464</v>
+      </c>
+      <c r="G58">
+        <v>0.116</v>
+      </c>
+      <c r="H58">
+        <v>11.7</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.46</v>
+      </c>
+      <c r="K58">
+        <v>0.46</v>
+      </c>
+      <c r="L58">
+        <v>2</v>
+      </c>
+      <c r="M58">
+        <v>0.5447232</v>
+      </c>
+      <c r="N58">
+        <v>1.4552768</v>
+      </c>
+      <c r="O58">
+        <v>0.2910553599999999</v>
+      </c>
+      <c r="P58">
+        <v>1.16422144</v>
+      </c>
+      <c r="Q58">
+        <v>1.62422144</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.3270607947717809</v>
+      </c>
+      <c r="T58">
+        <v>2.106598515808173</v>
+      </c>
+      <c r="U58">
+        <v>0.063</v>
+      </c>
+      <c r="V58">
+        <v>0.2</v>
+      </c>
+      <c r="W58">
+        <v>0.0504</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>3.671589533913739</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1719610858489088</v>
+      </c>
+      <c r="C59">
+        <v>8.157307381383523</v>
+      </c>
+      <c r="D59">
+        <v>16.84210738138352</v>
+      </c>
+      <c r="E59">
+        <v>5.0608</v>
+      </c>
+      <c r="F59">
+        <v>8.800800000000001</v>
+      </c>
+      <c r="G59">
+        <v>0.116</v>
+      </c>
+      <c r="H59">
+        <v>11.7</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.46</v>
+      </c>
+      <c r="K59">
+        <v>0.46</v>
+      </c>
+      <c r="L59">
+        <v>2</v>
+      </c>
+      <c r="M59">
+        <v>0.5544504</v>
+      </c>
+      <c r="N59">
+        <v>1.4455496</v>
+      </c>
+      <c r="O59">
+        <v>0.28910992</v>
+      </c>
+      <c r="P59">
+        <v>1.15643968</v>
+      </c>
+      <c r="Q59">
+        <v>1.61643968</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.3331001996486253</v>
+      </c>
+      <c r="T59">
+        <v>2.150734248383245</v>
+      </c>
+      <c r="U59">
+        <v>0.063</v>
+      </c>
+      <c r="V59">
+        <v>0.2</v>
+      </c>
+      <c r="W59">
+        <v>0.0504</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>3.607175682441567</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1717914219982341</v>
+      </c>
+      <c r="C60">
+        <v>8.024393705455173</v>
+      </c>
+      <c r="D60">
+        <v>16.86359370545517</v>
+      </c>
+      <c r="E60">
+        <v>5.215199999999999</v>
+      </c>
+      <c r="F60">
+        <v>8.9552</v>
+      </c>
+      <c r="G60">
+        <v>0.116</v>
+      </c>
+      <c r="H60">
+        <v>11.7</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.46</v>
+      </c>
+      <c r="K60">
+        <v>0.46</v>
+      </c>
+      <c r="L60">
+        <v>2</v>
+      </c>
+      <c r="M60">
+        <v>0.5641775999999999</v>
+      </c>
+      <c r="N60">
+        <v>1.4358224</v>
+      </c>
+      <c r="O60">
+        <v>0.2871644799999999</v>
+      </c>
+      <c r="P60">
+        <v>1.14865792</v>
+      </c>
+      <c r="Q60">
+        <v>1.60865792</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.3394271952338906</v>
+      </c>
+      <c r="T60">
+        <v>2.19697168250951</v>
+      </c>
+      <c r="U60">
+        <v>0.063</v>
+      </c>
+      <c r="V60">
+        <v>0.2</v>
+      </c>
+      <c r="W60">
+        <v>0.0504</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>3.544982998261541</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1749729581475594</v>
+      </c>
+      <c r="C61">
+        <v>7.47599379746095</v>
+      </c>
+      <c r="D61">
+        <v>16.46959379746095</v>
+      </c>
+      <c r="E61">
+        <v>5.369599999999998</v>
+      </c>
+      <c r="F61">
+        <v>9.109599999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.116</v>
+      </c>
+      <c r="H61">
+        <v>11.7</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.46</v>
+      </c>
+      <c r="K61">
+        <v>0.46</v>
+      </c>
+      <c r="L61">
+        <v>2</v>
+      </c>
+      <c r="M61">
+        <v>0.6385829599999998</v>
+      </c>
+      <c r="N61">
+        <v>1.36141704</v>
+      </c>
+      <c r="O61">
+        <v>0.2722834079999999</v>
+      </c>
+      <c r="P61">
+        <v>1.089133632</v>
+      </c>
+      <c r="Q61">
+        <v>1.549133632</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.3460628247501448</v>
+      </c>
+      <c r="T61">
+        <v>2.245464601227301</v>
+      </c>
+      <c r="U61">
+        <v>0.0701</v>
+      </c>
+      <c r="V61">
+        <v>0.2</v>
+      </c>
+      <c r="W61">
+        <v>0.05608</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>3.131934494462552</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1748600942968846</v>
+      </c>
+      <c r="C62">
+        <v>7.335255567906099</v>
+      </c>
+      <c r="D62">
+        <v>16.4832555679061</v>
+      </c>
+      <c r="E62">
+        <v>5.523999999999999</v>
+      </c>
+      <c r="F62">
+        <v>9.263999999999999</v>
+      </c>
+      <c r="G62">
+        <v>0.116</v>
+      </c>
+      <c r="H62">
+        <v>11.7</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.46</v>
+      </c>
+      <c r="K62">
+        <v>0.46</v>
+      </c>
+      <c r="L62">
+        <v>2</v>
+      </c>
+      <c r="M62">
+        <v>0.6494063999999999</v>
+      </c>
+      <c r="N62">
+        <v>1.3505936</v>
+      </c>
+      <c r="O62">
+        <v>0.27011872</v>
+      </c>
+      <c r="P62">
+        <v>1.08047488</v>
+      </c>
+      <c r="Q62">
+        <v>1.54047488</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.3530302357422116</v>
+      </c>
+      <c r="T62">
+        <v>2.296382165880981</v>
+      </c>
+      <c r="U62">
+        <v>0.0701</v>
+      </c>
+      <c r="V62">
+        <v>0.2</v>
+      </c>
+      <c r="W62">
+        <v>0.05608</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>3.079735586221509</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1747472304462099</v>
+      </c>
+      <c r="C63">
+        <v>7.194540022447354</v>
+      </c>
+      <c r="D63">
+        <v>16.49694002244735</v>
+      </c>
+      <c r="E63">
+        <v>5.6784</v>
+      </c>
+      <c r="F63">
+        <v>9.4184</v>
+      </c>
+      <c r="G63">
+        <v>0.116</v>
+      </c>
+      <c r="H63">
+        <v>11.7</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.46</v>
+      </c>
+      <c r="K63">
+        <v>0.46</v>
+      </c>
+      <c r="L63">
+        <v>2</v>
+      </c>
+      <c r="M63">
+        <v>0.66022984</v>
+      </c>
+      <c r="N63">
+        <v>1.33977016</v>
+      </c>
+      <c r="O63">
+        <v>0.267954032</v>
+      </c>
+      <c r="P63">
+        <v>1.071816128</v>
+      </c>
+      <c r="Q63">
+        <v>1.531816128</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.3603549498620767</v>
+      </c>
+      <c r="T63">
+        <v>2.349910887696389</v>
+      </c>
+      <c r="U63">
+        <v>0.0701</v>
+      </c>
+      <c r="V63">
+        <v>0.2</v>
+      </c>
+      <c r="W63">
+        <v>0.05608</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>3.029248117594928</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1851991665955351</v>
+      </c>
+      <c r="C64">
+        <v>5.862367171798306</v>
+      </c>
+      <c r="D64">
+        <v>15.31916717179831</v>
+      </c>
+      <c r="E64">
+        <v>5.832799999999999</v>
+      </c>
+      <c r="F64">
+        <v>9.572799999999999</v>
+      </c>
+      <c r="G64">
+        <v>0.116</v>
+      </c>
+      <c r="H64">
+        <v>11.7</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.46</v>
+      </c>
+      <c r="K64">
+        <v>0.46</v>
+      </c>
+      <c r="L64">
+        <v>2</v>
+      </c>
+      <c r="M64">
+        <v>0.8749539200000001</v>
+      </c>
+      <c r="N64">
+        <v>1.12504608</v>
+      </c>
+      <c r="O64">
+        <v>0.2250092159999999</v>
+      </c>
+      <c r="P64">
+        <v>0.900036864</v>
+      </c>
+      <c r="Q64">
+        <v>1.360036864</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.3680651752514083</v>
+      </c>
+      <c r="T64">
+        <v>2.406256910659976</v>
+      </c>
+      <c r="U64">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V64">
+        <v>0.2</v>
+      </c>
+      <c r="W64">
+        <v>0.07312</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>2.285834664298664</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1852567027448604</v>
+      </c>
+      <c r="C65">
+        <v>5.701948970695751</v>
+      </c>
+      <c r="D65">
+        <v>15.31314897069575</v>
+      </c>
+      <c r="E65">
+        <v>5.9872</v>
+      </c>
+      <c r="F65">
+        <v>9.7272</v>
+      </c>
+      <c r="G65">
+        <v>0.116</v>
+      </c>
+      <c r="H65">
+        <v>11.7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.46</v>
+      </c>
+      <c r="K65">
+        <v>0.46</v>
+      </c>
+      <c r="L65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>0.8890660800000001</v>
+      </c>
+      <c r="N65">
+        <v>1.11093392</v>
+      </c>
+      <c r="O65">
+        <v>0.2221867839999999</v>
+      </c>
+      <c r="P65">
+        <v>0.888747136</v>
+      </c>
+      <c r="Q65">
+        <v>1.348747136</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.3761921695807038</v>
+      </c>
+      <c r="T65">
+        <v>2.465648664594567</v>
+      </c>
+      <c r="U65">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V65">
+        <v>0.2</v>
+      </c>
+      <c r="W65">
+        <v>0.07312</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>2.249551574389161</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1853142388941857</v>
+      </c>
+      <c r="C66">
+        <v>5.541535496288978</v>
+      </c>
+      <c r="D66">
+        <v>15.30713549628898</v>
+      </c>
+      <c r="E66">
+        <v>6.1416</v>
+      </c>
+      <c r="F66">
+        <v>9.881600000000001</v>
+      </c>
+      <c r="G66">
+        <v>0.116</v>
+      </c>
+      <c r="H66">
+        <v>11.7</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.46</v>
+      </c>
+      <c r="K66">
+        <v>0.46</v>
+      </c>
+      <c r="L66">
+        <v>2</v>
+      </c>
+      <c r="M66">
+        <v>0.9031782400000001</v>
+      </c>
+      <c r="N66">
+        <v>1.09682176</v>
+      </c>
+      <c r="O66">
+        <v>0.2193643519999999</v>
+      </c>
+      <c r="P66">
+        <v>0.8774574079999999</v>
+      </c>
+      <c r="Q66">
+        <v>1.337457408</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.3847706635949603</v>
+      </c>
+      <c r="T66">
+        <v>2.528339960414414</v>
+      </c>
+      <c r="U66">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V66">
+        <v>0.2</v>
+      </c>
+      <c r="W66">
+        <v>0.07312</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>2.21440233103933</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1853717750435109</v>
+      </c>
+      <c r="C67">
+        <v>5.381126743011652</v>
+      </c>
+      <c r="D67">
+        <v>15.30112674301165</v>
+      </c>
+      <c r="E67">
+        <v>6.295999999999999</v>
+      </c>
+      <c r="F67">
+        <v>10.036</v>
+      </c>
+      <c r="G67">
+        <v>0.116</v>
+      </c>
+      <c r="H67">
+        <v>11.7</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.46</v>
+      </c>
+      <c r="K67">
+        <v>0.46</v>
+      </c>
+      <c r="L67">
+        <v>2</v>
+      </c>
+      <c r="M67">
+        <v>0.9172904000000001</v>
+      </c>
+      <c r="N67">
+        <v>1.0827096</v>
+      </c>
+      <c r="O67">
+        <v>0.2165419199999999</v>
+      </c>
+      <c r="P67">
+        <v>0.8661676799999999</v>
+      </c>
+      <c r="Q67">
+        <v>1.32616768</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.3938393572671741</v>
+      </c>
+      <c r="T67">
+        <v>2.594613615995395</v>
+      </c>
+      <c r="U67">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V67">
+        <v>0.2</v>
+      </c>
+      <c r="W67">
+        <v>0.07312</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>2.180334602869495</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1854293111928362</v>
+      </c>
+      <c r="C68">
+        <v>5.220722705306169</v>
+      </c>
+      <c r="D68">
+        <v>15.29512270530617</v>
+      </c>
+      <c r="E68">
+        <v>6.4504</v>
+      </c>
+      <c r="F68">
+        <v>10.1904</v>
+      </c>
+      <c r="G68">
+        <v>0.116</v>
+      </c>
+      <c r="H68">
+        <v>11.7</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.46</v>
+      </c>
+      <c r="K68">
+        <v>0.46</v>
+      </c>
+      <c r="L68">
+        <v>2</v>
+      </c>
+      <c r="M68">
+        <v>0.9314025600000001</v>
+      </c>
+      <c r="N68">
+        <v>1.06859744</v>
+      </c>
+      <c r="O68">
+        <v>0.213719488</v>
+      </c>
+      <c r="P68">
+        <v>0.8548779520000001</v>
+      </c>
+      <c r="Q68">
+        <v>1.314877952</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.4034415035083418</v>
+      </c>
+      <c r="T68">
+        <v>2.664785721904668</v>
+      </c>
+      <c r="U68">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V68">
+        <v>0.2</v>
+      </c>
+      <c r="W68">
+        <v>0.07312</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>2.147299230098745</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1854868473421615</v>
+      </c>
+      <c r="C69">
+        <v>5.06032337762365</v>
+      </c>
+      <c r="D69">
+        <v>15.28912337762365</v>
+      </c>
+      <c r="E69">
+        <v>6.604800000000001</v>
+      </c>
+      <c r="F69">
+        <v>10.3448</v>
+      </c>
+      <c r="G69">
+        <v>0.116</v>
+      </c>
+      <c r="H69">
+        <v>11.7</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.46</v>
+      </c>
+      <c r="K69">
+        <v>0.46</v>
+      </c>
+      <c r="L69">
+        <v>2</v>
+      </c>
+      <c r="M69">
+        <v>0.9455147200000001</v>
+      </c>
+      <c r="N69">
+        <v>1.05448528</v>
+      </c>
+      <c r="O69">
+        <v>0.2108970559999999</v>
+      </c>
+      <c r="P69">
+        <v>0.8435882239999999</v>
+      </c>
+      <c r="Q69">
+        <v>1.303588224</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.41362559800655</v>
+      </c>
+      <c r="T69">
+        <v>2.739210682717535</v>
+      </c>
+      <c r="U69">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V69">
+        <v>0.2</v>
+      </c>
+      <c r="W69">
+        <v>0.07312</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>2.115249987858465</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1855443834914867</v>
+      </c>
+      <c r="C70">
+        <v>4.89992875442393</v>
+      </c>
+      <c r="D70">
+        <v>15.28312875442393</v>
+      </c>
+      <c r="E70">
+        <v>6.7592</v>
+      </c>
+      <c r="F70">
+        <v>10.4992</v>
+      </c>
+      <c r="G70">
+        <v>0.116</v>
+      </c>
+      <c r="H70">
+        <v>11.7</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.46</v>
+      </c>
+      <c r="K70">
+        <v>0.46</v>
+      </c>
+      <c r="L70">
+        <v>2</v>
+      </c>
+      <c r="M70">
+        <v>0.9596268800000001</v>
+      </c>
+      <c r="N70">
+        <v>1.04037312</v>
+      </c>
+      <c r="O70">
+        <v>0.2080746239999999</v>
+      </c>
+      <c r="P70">
+        <v>0.8322984959999999</v>
+      </c>
+      <c r="Q70">
+        <v>1.292298496</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.424446198410896</v>
+      </c>
+      <c r="T70">
+        <v>2.818287203581205</v>
+      </c>
+      <c r="U70">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V70">
+        <v>0.2</v>
+      </c>
+      <c r="W70">
+        <v>0.07312</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>2.084143370389958</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.185601919640812</v>
+      </c>
+      <c r="C71">
+        <v>4.739538830175501</v>
+      </c>
+      <c r="D71">
+        <v>15.2771388301755</v>
+      </c>
+      <c r="E71">
+        <v>6.913600000000001</v>
+      </c>
+      <c r="F71">
+        <v>10.6536</v>
+      </c>
+      <c r="G71">
+        <v>0.116</v>
+      </c>
+      <c r="H71">
+        <v>11.7</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.46</v>
+      </c>
+      <c r="K71">
+        <v>0.46</v>
+      </c>
+      <c r="L71">
+        <v>2</v>
+      </c>
+      <c r="M71">
+        <v>0.9737390400000002</v>
+      </c>
+      <c r="N71">
+        <v>1.02626096</v>
+      </c>
+      <c r="O71">
+        <v>0.2052521919999999</v>
+      </c>
+      <c r="P71">
+        <v>0.8210087679999998</v>
+      </c>
+      <c r="Q71">
+        <v>1.281008768</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.4359649020671356</v>
+      </c>
+      <c r="T71">
+        <v>2.902465435468338</v>
+      </c>
+      <c r="U71">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V71">
+        <v>0.2</v>
+      </c>
+      <c r="W71">
+        <v>0.07312</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>2.053938394007495</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1856594557901373</v>
+      </c>
+      <c r="C72">
+        <v>4.579153599355557</v>
+      </c>
+      <c r="D72">
+        <v>15.27115359935556</v>
+      </c>
+      <c r="E72">
+        <v>7.068</v>
+      </c>
+      <c r="F72">
+        <v>10.808</v>
+      </c>
+      <c r="G72">
+        <v>0.116</v>
+      </c>
+      <c r="H72">
+        <v>11.7</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.46</v>
+      </c>
+      <c r="K72">
+        <v>0.46</v>
+      </c>
+      <c r="L72">
+        <v>2</v>
+      </c>
+      <c r="M72">
+        <v>0.9878512</v>
+      </c>
+      <c r="N72">
+        <v>1.0121488</v>
+      </c>
+      <c r="O72">
+        <v>0.2024297599999999</v>
+      </c>
+      <c r="P72">
+        <v>0.8097190399999999</v>
+      </c>
+      <c r="Q72">
+        <v>1.26971904</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.4482515193004576</v>
+      </c>
+      <c r="T72">
+        <v>2.992255549481279</v>
+      </c>
+      <c r="U72">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V72">
+        <v>0.2</v>
+      </c>
+      <c r="W72">
+        <v>0.07312</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>2.024596416950245</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1977017919394625</v>
+      </c>
+      <c r="C73">
+        <v>3.267432698270444</v>
+      </c>
+      <c r="D73">
+        <v>14.11383269827044</v>
+      </c>
+      <c r="E73">
+        <v>7.222399999999999</v>
+      </c>
+      <c r="F73">
+        <v>10.9624</v>
+      </c>
+      <c r="G73">
+        <v>0.116</v>
+      </c>
+      <c r="H73">
+        <v>11.7</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.46</v>
+      </c>
+      <c r="K73">
+        <v>0.46</v>
+      </c>
+      <c r="L73">
+        <v>2</v>
+      </c>
+      <c r="M73">
+        <v>1.23327</v>
+      </c>
+      <c r="N73">
+        <v>0.7667300000000001</v>
+      </c>
+      <c r="O73">
+        <v>0.153346</v>
+      </c>
+      <c r="P73">
+        <v>0.6133840000000002</v>
+      </c>
+      <c r="Q73">
+        <v>1.073384</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.4613854894464224</v>
+      </c>
+      <c r="T73">
+        <v>3.088238085150285</v>
+      </c>
+      <c r="U73">
+        <v>0.1125</v>
+      </c>
+      <c r="V73">
+        <v>0.2</v>
+      </c>
+      <c r="W73">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>1.621704898359646</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1979281280887878</v>
+      </c>
+      <c r="C74">
+        <v>3.092957865596203</v>
+      </c>
+      <c r="D74">
+        <v>14.0937578655962</v>
+      </c>
+      <c r="E74">
+        <v>7.376799999999999</v>
+      </c>
+      <c r="F74">
+        <v>11.1168</v>
+      </c>
+      <c r="G74">
+        <v>0.116</v>
+      </c>
+      <c r="H74">
+        <v>11.7</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.46</v>
+      </c>
+      <c r="K74">
+        <v>0.46</v>
+      </c>
+      <c r="L74">
+        <v>2</v>
+      </c>
+      <c r="M74">
+        <v>1.25064</v>
+      </c>
+      <c r="N74">
+        <v>0.74936</v>
+      </c>
+      <c r="O74">
+        <v>0.149872</v>
+      </c>
+      <c r="P74">
+        <v>0.599488</v>
+      </c>
+      <c r="Q74">
+        <v>1.059488</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.4754576003170992</v>
+      </c>
+      <c r="T74">
+        <v>3.191076516224221</v>
+      </c>
+      <c r="U74">
+        <v>0.1125</v>
+      </c>
+      <c r="V74">
+        <v>0.2</v>
+      </c>
+      <c r="W74">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>1.599181219215762</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.198154464238113</v>
+      </c>
+      <c r="C75">
+        <v>2.918540058752368</v>
+      </c>
+      <c r="D75">
+        <v>14.07374005875237</v>
+      </c>
+      <c r="E75">
+        <v>7.531199999999998</v>
+      </c>
+      <c r="F75">
+        <v>11.2712</v>
+      </c>
+      <c r="G75">
+        <v>0.116</v>
+      </c>
+      <c r="H75">
+        <v>11.7</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.46</v>
+      </c>
+      <c r="K75">
+        <v>0.46</v>
+      </c>
+      <c r="L75">
+        <v>2</v>
+      </c>
+      <c r="M75">
+        <v>1.26801</v>
+      </c>
+      <c r="N75">
+        <v>0.7319900000000001</v>
+      </c>
+      <c r="O75">
+        <v>0.146398</v>
+      </c>
+      <c r="P75">
+        <v>0.5855920000000001</v>
+      </c>
+      <c r="Q75">
+        <v>1.045592</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.4905720897707889</v>
+      </c>
+      <c r="T75">
+        <v>3.301532608859188</v>
+      </c>
+      <c r="U75">
+        <v>0.1125</v>
+      </c>
+      <c r="V75">
+        <v>0.2</v>
+      </c>
+      <c r="W75">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>1.57727462717171</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1983808003874383</v>
+      </c>
+      <c r="C76">
+        <v>2.744179035096831</v>
+      </c>
+      <c r="D76">
+        <v>14.05377903509683</v>
+      </c>
+      <c r="E76">
+        <v>7.685599999999999</v>
+      </c>
+      <c r="F76">
+        <v>11.4256</v>
+      </c>
+      <c r="G76">
+        <v>0.116</v>
+      </c>
+      <c r="H76">
+        <v>11.7</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.46</v>
+      </c>
+      <c r="K76">
+        <v>0.46</v>
+      </c>
+      <c r="L76">
+        <v>2</v>
+      </c>
+      <c r="M76">
+        <v>1.28538</v>
+      </c>
+      <c r="N76">
+        <v>0.71462</v>
+      </c>
+      <c r="O76">
+        <v>0.142924</v>
+      </c>
+      <c r="P76">
+        <v>0.5716960000000001</v>
+      </c>
+      <c r="Q76">
+        <v>1.031696</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.5068492322593781</v>
+      </c>
+      <c r="T76">
+        <v>3.420485324004539</v>
+      </c>
+      <c r="U76">
+        <v>0.1125</v>
+      </c>
+      <c r="V76">
+        <v>0.2</v>
+      </c>
+      <c r="W76">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>1.555960105182903</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1986071365367636</v>
+      </c>
+      <c r="C77">
+        <v>2.569874553362126</v>
+      </c>
+      <c r="D77">
+        <v>14.03387455336213</v>
+      </c>
+      <c r="E77">
+        <v>7.84</v>
+      </c>
+      <c r="F77">
+        <v>11.58</v>
+      </c>
+      <c r="G77">
+        <v>0.116</v>
+      </c>
+      <c r="H77">
+        <v>11.7</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.46</v>
+      </c>
+      <c r="K77">
+        <v>0.46</v>
+      </c>
+      <c r="L77">
+        <v>2</v>
+      </c>
+      <c r="M77">
+        <v>1.30275</v>
+      </c>
+      <c r="N77">
+        <v>0.6972499999999999</v>
+      </c>
+      <c r="O77">
+        <v>0.13945</v>
+      </c>
+      <c r="P77">
+        <v>0.5578</v>
+      </c>
+      <c r="Q77">
+        <v>1.0178</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.5244285461470543</v>
+      </c>
+      <c r="T77">
+        <v>3.548954256361517</v>
+      </c>
+      <c r="U77">
+        <v>0.1125</v>
+      </c>
+      <c r="V77">
+        <v>0.2</v>
+      </c>
+      <c r="W77">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>1.535213970447131</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1988334726860888</v>
+      </c>
+      <c r="C78">
+        <v>2.395626373645673</v>
+      </c>
+      <c r="D78">
+        <v>14.01402637364567</v>
+      </c>
+      <c r="E78">
+        <v>7.994399999999999</v>
+      </c>
+      <c r="F78">
+        <v>11.7344</v>
+      </c>
+      <c r="G78">
+        <v>0.116</v>
+      </c>
+      <c r="H78">
+        <v>11.7</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.46</v>
+      </c>
+      <c r="K78">
+        <v>0.46</v>
+      </c>
+      <c r="L78">
+        <v>2</v>
+      </c>
+      <c r="M78">
+        <v>1.32012</v>
+      </c>
+      <c r="N78">
+        <v>0.67988</v>
+      </c>
+      <c r="O78">
+        <v>0.135976</v>
+      </c>
+      <c r="P78">
+        <v>0.5439040000000001</v>
+      </c>
+      <c r="Q78">
+        <v>1.003904</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.5434728028587035</v>
+      </c>
+      <c r="T78">
+        <v>3.688128933081576</v>
+      </c>
+      <c r="U78">
+        <v>0.1125</v>
+      </c>
+      <c r="V78">
+        <v>0.2</v>
+      </c>
+      <c r="W78">
+        <v>0.09000000000000001</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>1.515013786625458</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2584096791762874</v>
+      </c>
+      <c r="C79">
+        <v>-1.56053014331186</v>
+      </c>
+      <c r="D79">
+        <v>10.21226985668814</v>
+      </c>
+      <c r="E79">
+        <v>8.1488</v>
+      </c>
+      <c r="F79">
+        <v>11.8888</v>
+      </c>
+      <c r="G79">
+        <v>0.116</v>
+      </c>
+      <c r="H79">
+        <v>11.7</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.46</v>
+      </c>
+      <c r="K79">
+        <v>0.46</v>
+      </c>
+      <c r="L79">
+        <v>2</v>
+      </c>
+      <c r="M79">
+        <v>2.33733808</v>
+      </c>
+      <c r="N79">
+        <v>-0.3373380799999999</v>
+      </c>
+      <c r="O79">
+        <v>-0.06746761599999997</v>
+      </c>
+      <c r="P79">
+        <v>-0.2698704639999999</v>
+      </c>
+      <c r="Q79">
+        <v>0.190129536</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.5779757170764468</v>
+      </c>
+      <c r="T79">
+        <v>3.940274868985552</v>
+      </c>
+      <c r="U79">
+        <v>0.1966</v>
+      </c>
+      <c r="V79">
+        <v>0.1711348492640825</v>
+      </c>
+      <c r="W79">
+        <v>0.1629548886346814</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.8556742463204126</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2599876791762874</v>
+      </c>
+      <c r="C80">
+        <v>-1.787786650934105</v>
+      </c>
+      <c r="D80">
+        <v>10.1394133490659</v>
+      </c>
+      <c r="E80">
+        <v>8.3032</v>
+      </c>
+      <c r="F80">
+        <v>12.0432</v>
+      </c>
+      <c r="G80">
+        <v>0.116</v>
+      </c>
+      <c r="H80">
+        <v>11.7</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.46</v>
+      </c>
+      <c r="K80">
+        <v>0.46</v>
+      </c>
+      <c r="L80">
+        <v>2</v>
+      </c>
+      <c r="M80">
+        <v>2.36769312</v>
+      </c>
+      <c r="N80">
+        <v>-0.3676931200000002</v>
+      </c>
+      <c r="O80">
+        <v>-0.07353862400000002</v>
+      </c>
+      <c r="P80">
+        <v>-0.2941544960000002</v>
+      </c>
+      <c r="Q80">
+        <v>0.1658455039999998</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.6024837042162852</v>
+      </c>
+      <c r="T80">
+        <v>4.119378272121259</v>
+      </c>
+      <c r="U80">
+        <v>0.1966</v>
+      </c>
+      <c r="V80">
+        <v>0.1689408127350558</v>
+      </c>
+      <c r="W80">
+        <v>0.163386236216288</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.8447040636752789</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2615656791762874</v>
+      </c>
+      <c r="C81">
+        <v>-2.014010974698826</v>
+      </c>
+      <c r="D81">
+        <v>10.06758902530117</v>
+      </c>
+      <c r="E81">
+        <v>8.457599999999999</v>
+      </c>
+      <c r="F81">
+        <v>12.1976</v>
+      </c>
+      <c r="G81">
+        <v>0.116</v>
+      </c>
+      <c r="H81">
+        <v>11.7</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.46</v>
+      </c>
+      <c r="K81">
+        <v>0.46</v>
+      </c>
+      <c r="L81">
+        <v>2</v>
+      </c>
+      <c r="M81">
+        <v>2.39804816</v>
+      </c>
+      <c r="N81">
+        <v>-0.3980481600000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.079609632</v>
+      </c>
+      <c r="P81">
+        <v>-0.3184385280000001</v>
+      </c>
+      <c r="Q81">
+        <v>0.1415614719999999</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.6293257853694416</v>
+      </c>
+      <c r="T81">
+        <v>4.315539142222272</v>
+      </c>
+      <c r="U81">
+        <v>0.1966</v>
+      </c>
+      <c r="V81">
+        <v>0.166802321434612</v>
+      </c>
+      <c r="W81">
+        <v>0.1638066636059553</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.8340116071730602</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2631436791762874</v>
+      </c>
+      <c r="C82">
+        <v>-2.239224895288238</v>
+      </c>
+      <c r="D82">
+        <v>9.996775104711762</v>
+      </c>
+      <c r="E82">
+        <v>8.612</v>
+      </c>
+      <c r="F82">
+        <v>12.352</v>
+      </c>
+      <c r="G82">
+        <v>0.116</v>
+      </c>
+      <c r="H82">
+        <v>11.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.46</v>
+      </c>
+      <c r="K82">
+        <v>0.46</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="M82">
+        <v>2.4284032</v>
+      </c>
+      <c r="N82">
+        <v>-0.4284032</v>
+      </c>
+      <c r="O82">
+        <v>-0.08568063999999997</v>
+      </c>
+      <c r="P82">
+        <v>-0.34272256</v>
+      </c>
+      <c r="Q82">
+        <v>0.11727744</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.6588520746379138</v>
+      </c>
+      <c r="T82">
+        <v>4.531316099333385</v>
+      </c>
+      <c r="U82">
+        <v>0.1966</v>
+      </c>
+      <c r="V82">
+        <v>0.1647172924166794</v>
+      </c>
+      <c r="W82">
+        <v>0.1642165803108808</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.823586462083397</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2647216791762874</v>
+      </c>
+      <c r="C83">
+        <v>-2.463449584856544</v>
+      </c>
+      <c r="D83">
+        <v>9.926950415143457</v>
+      </c>
+      <c r="E83">
+        <v>8.766400000000001</v>
+      </c>
+      <c r="F83">
+        <v>12.5064</v>
+      </c>
+      <c r="G83">
+        <v>0.116</v>
+      </c>
+      <c r="H83">
+        <v>11.7</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.46</v>
+      </c>
+      <c r="K83">
+        <v>0.46</v>
+      </c>
+      <c r="L83">
+        <v>2</v>
+      </c>
+      <c r="M83">
+        <v>2.45875824</v>
+      </c>
+      <c r="N83">
+        <v>-0.4587582400000003</v>
+      </c>
+      <c r="O83">
+        <v>-0.09175164800000005</v>
+      </c>
+      <c r="P83">
+        <v>-0.3670065920000003</v>
+      </c>
+      <c r="Q83">
+        <v>0.09299340799999967</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.6914863943556986</v>
+      </c>
+      <c r="T83">
+        <v>4.769806420350932</v>
+      </c>
+      <c r="U83">
+        <v>0.1966</v>
+      </c>
+      <c r="V83">
+        <v>0.1626837455967204</v>
+      </c>
+      <c r="W83">
+        <v>0.1646163756156848</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.8134187279836019</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2662996791762874</v>
+      </c>
+      <c r="C84">
+        <v>-2.686705628134556</v>
+      </c>
+      <c r="D84">
+        <v>9.858094371865445</v>
+      </c>
+      <c r="E84">
+        <v>8.9208</v>
+      </c>
+      <c r="F84">
+        <v>12.6608</v>
+      </c>
+      <c r="G84">
+        <v>0.116</v>
+      </c>
+      <c r="H84">
+        <v>11.7</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.46</v>
+      </c>
+      <c r="K84">
+        <v>0.46</v>
+      </c>
+      <c r="L84">
+        <v>2</v>
+      </c>
+      <c r="M84">
+        <v>2.48911328</v>
+      </c>
+      <c r="N84">
+        <v>-0.4891132799999998</v>
+      </c>
+      <c r="O84">
+        <v>-0.09782265599999992</v>
+      </c>
+      <c r="P84">
+        <v>-0.3912906239999998</v>
+      </c>
+      <c r="Q84">
+        <v>0.06870937600000016</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.7277467495976822</v>
+      </c>
+      <c r="T84">
+        <v>5.034795665925984</v>
+      </c>
+      <c r="U84">
+        <v>0.1966</v>
+      </c>
+      <c r="V84">
+        <v>0.1606997974796872</v>
+      </c>
+      <c r="W84">
+        <v>0.1650064198154935</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.8034989873984362</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2836678512017706</v>
+      </c>
+      <c r="C85">
+        <v>-3.540327996663956</v>
+      </c>
+      <c r="D85">
+        <v>9.158872003336045</v>
+      </c>
+      <c r="E85">
+        <v>9.075200000000001</v>
+      </c>
+      <c r="F85">
+        <v>12.8152</v>
+      </c>
+      <c r="G85">
+        <v>0.116</v>
+      </c>
+      <c r="H85">
+        <v>11.7</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.46</v>
+      </c>
+      <c r="K85">
+        <v>0.46</v>
+      </c>
+      <c r="L85">
+        <v>2</v>
+      </c>
+      <c r="M85">
+        <v>2.73988976</v>
+      </c>
+      <c r="N85">
+        <v>-0.7398897600000001</v>
+      </c>
+      <c r="O85">
+        <v>-0.147977952</v>
+      </c>
+      <c r="P85">
+        <v>-0.5919118080000001</v>
+      </c>
+      <c r="Q85">
+        <v>-0.1319118080000001</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.7771799232533296</v>
+      </c>
+      <c r="T85">
+        <v>5.396051348777759</v>
+      </c>
+      <c r="U85">
+        <v>0.2138</v>
+      </c>
+      <c r="V85">
+        <v>0.1459912752110143</v>
+      </c>
+      <c r="W85">
+        <v>0.1825870653598851</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.7299563760550716</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2854178512017707</v>
+      </c>
+      <c r="C86">
+        <v>-3.759719342293375</v>
+      </c>
+      <c r="D86">
+        <v>9.093880657706626</v>
+      </c>
+      <c r="E86">
+        <v>9.2296</v>
+      </c>
+      <c r="F86">
+        <v>12.9696</v>
+      </c>
+      <c r="G86">
+        <v>0.116</v>
+      </c>
+      <c r="H86">
+        <v>11.7</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.46</v>
+      </c>
+      <c r="K86">
+        <v>0.46</v>
+      </c>
+      <c r="L86">
+        <v>2</v>
+      </c>
+      <c r="M86">
+        <v>2.77290048</v>
+      </c>
+      <c r="N86">
+        <v>-0.7729004799999997</v>
+      </c>
+      <c r="O86">
+        <v>-0.1545800959999999</v>
+      </c>
+      <c r="P86">
+        <v>-0.6183203839999998</v>
+      </c>
+      <c r="Q86">
+        <v>-0.1583203839999998</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.8233286684566623</v>
+      </c>
+      <c r="T86">
+        <v>5.733304558076366</v>
+      </c>
+      <c r="U86">
+        <v>0.2138</v>
+      </c>
+      <c r="V86">
+        <v>0.1442532838394546</v>
+      </c>
+      <c r="W86">
+        <v>0.1829586479151246</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.7212664191972733</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2871678512017707</v>
+      </c>
+      <c r="C87">
+        <v>-3.978194829817152</v>
+      </c>
+      <c r="D87">
+        <v>9.029805170182847</v>
+      </c>
+      <c r="E87">
+        <v>9.383999999999999</v>
+      </c>
+      <c r="F87">
+        <v>13.124</v>
+      </c>
+      <c r="G87">
+        <v>0.116</v>
+      </c>
+      <c r="H87">
+        <v>11.7</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.46</v>
+      </c>
+      <c r="K87">
+        <v>0.46</v>
+      </c>
+      <c r="L87">
+        <v>2</v>
+      </c>
+      <c r="M87">
+        <v>2.8059112</v>
+      </c>
+      <c r="N87">
+        <v>-0.8059111999999997</v>
+      </c>
+      <c r="O87">
+        <v>-0.1611822399999999</v>
+      </c>
+      <c r="P87">
+        <v>-0.6447289599999998</v>
+      </c>
+      <c r="Q87">
+        <v>-0.1847289599999998</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.8756305796871064</v>
+      </c>
+      <c r="T87">
+        <v>6.115524861948123</v>
+      </c>
+      <c r="U87">
+        <v>0.2138</v>
+      </c>
+      <c r="V87">
+        <v>0.1425561863825199</v>
+      </c>
+      <c r="W87">
+        <v>0.1833214873514172</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.7127809319125995</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2889178512017707</v>
+      </c>
+      <c r="C88">
+        <v>-4.195773683193243</v>
+      </c>
+      <c r="D88">
+        <v>8.966626316806757</v>
+      </c>
+      <c r="E88">
+        <v>9.538399999999999</v>
+      </c>
+      <c r="F88">
+        <v>13.2784</v>
+      </c>
+      <c r="G88">
+        <v>0.116</v>
+      </c>
+      <c r="H88">
+        <v>11.7</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.46</v>
+      </c>
+      <c r="K88">
+        <v>0.46</v>
+      </c>
+      <c r="L88">
+        <v>2</v>
+      </c>
+      <c r="M88">
+        <v>2.83892192</v>
+      </c>
+      <c r="N88">
+        <v>-0.8389219199999998</v>
+      </c>
+      <c r="O88">
+        <v>-0.1677843839999999</v>
+      </c>
+      <c r="P88">
+        <v>-0.6711375359999998</v>
+      </c>
+      <c r="Q88">
+        <v>-0.2111375359999998</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.9354041925218999</v>
+      </c>
+      <c r="T88">
+        <v>6.55234806637299</v>
+      </c>
+      <c r="U88">
+        <v>0.2138</v>
+      </c>
+      <c r="V88">
+        <v>0.1408985563083045</v>
+      </c>
+      <c r="W88">
+        <v>0.1836758886612845</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.7044927815415227</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2906678512017706</v>
+      </c>
+      <c r="C89">
+        <v>-4.412474592100594</v>
+      </c>
+      <c r="D89">
+        <v>8.904325407899407</v>
+      </c>
+      <c r="E89">
+        <v>9.6928</v>
+      </c>
+      <c r="F89">
+        <v>13.4328</v>
+      </c>
+      <c r="G89">
+        <v>0.116</v>
+      </c>
+      <c r="H89">
+        <v>11.7</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.46</v>
+      </c>
+      <c r="K89">
+        <v>0.46</v>
+      </c>
+      <c r="L89">
+        <v>2</v>
+      </c>
+      <c r="M89">
+        <v>2.87193264</v>
+      </c>
+      <c r="N89">
+        <v>-0.8719326399999998</v>
+      </c>
+      <c r="O89">
+        <v>-0.1743865279999999</v>
+      </c>
+      <c r="P89">
+        <v>-0.6975461119999999</v>
+      </c>
+      <c r="Q89">
+        <v>-0.237546112</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>1.004373745792815</v>
+      </c>
+      <c r="T89">
+        <v>7.056374840709373</v>
+      </c>
+      <c r="U89">
+        <v>0.2138</v>
+      </c>
+      <c r="V89">
+        <v>0.1392790326725769</v>
+      </c>
+      <c r="W89">
+        <v>0.1840221428146031</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.6963951633628844</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2924178512017707</v>
+      </c>
+      <c r="C90">
+        <v>-4.628315730372156</v>
+      </c>
+      <c r="D90">
+        <v>8.842884269627843</v>
+      </c>
+      <c r="E90">
+        <v>9.847199999999999</v>
+      </c>
+      <c r="F90">
+        <v>13.5872</v>
+      </c>
+      <c r="G90">
+        <v>0.116</v>
+      </c>
+      <c r="H90">
+        <v>11.7</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.46</v>
+      </c>
+      <c r="K90">
+        <v>0.46</v>
+      </c>
+      <c r="L90">
+        <v>2</v>
+      </c>
+      <c r="M90">
+        <v>2.90494336</v>
+      </c>
+      <c r="N90">
+        <v>-0.9049433599999999</v>
+      </c>
+      <c r="O90">
+        <v>-0.1809886719999999</v>
+      </c>
+      <c r="P90">
+        <v>-0.723954688</v>
+      </c>
+      <c r="Q90">
+        <v>-0.263954688</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>1.084838224608883</v>
+      </c>
+      <c r="T90">
+        <v>7.644406077435156</v>
+      </c>
+      <c r="U90">
+        <v>0.2138</v>
+      </c>
+      <c r="V90">
+        <v>0.1376963163922067</v>
+      </c>
+      <c r="W90">
+        <v>0.1843605275553462</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.6884815819610335</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2941678512017706</v>
+      </c>
+      <c r="C91">
+        <v>-4.843314773669979</v>
+      </c>
+      <c r="D91">
+        <v>8.782285226330021</v>
+      </c>
+      <c r="E91">
+        <v>10.0016</v>
+      </c>
+      <c r="F91">
+        <v>13.7416</v>
+      </c>
+      <c r="G91">
+        <v>0.116</v>
+      </c>
+      <c r="H91">
+        <v>11.7</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.46</v>
+      </c>
+      <c r="K91">
+        <v>0.46</v>
+      </c>
+      <c r="L91">
+        <v>2</v>
+      </c>
+      <c r="M91">
+        <v>2.93795408</v>
+      </c>
+      <c r="N91">
+        <v>-0.9379540799999999</v>
+      </c>
+      <c r="O91">
+        <v>-0.1875908159999999</v>
+      </c>
+      <c r="P91">
+        <v>-0.750363264</v>
+      </c>
+      <c r="Q91">
+        <v>-0.290363264</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>1.179932608664236</v>
+      </c>
+      <c r="T91">
+        <v>8.339352084474715</v>
+      </c>
+      <c r="U91">
+        <v>0.2138</v>
+      </c>
+      <c r="V91">
+        <v>0.1361491667698223</v>
+      </c>
+      <c r="W91">
+        <v>0.184691308144612</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.6807458338491118</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2959178512017707</v>
+      </c>
+      <c r="C92">
+        <v>-5.057488916438531</v>
+      </c>
+      <c r="D92">
+        <v>8.722511083561468</v>
+      </c>
+      <c r="E92">
+        <v>10.156</v>
+      </c>
+      <c r="F92">
+        <v>13.896</v>
+      </c>
+      <c r="G92">
+        <v>0.116</v>
+      </c>
+      <c r="H92">
+        <v>11.7</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.46</v>
+      </c>
+      <c r="K92">
+        <v>0.46</v>
+      </c>
+      <c r="L92">
+        <v>2</v>
+      </c>
+      <c r="M92">
+        <v>2.9709648</v>
+      </c>
+      <c r="N92">
+        <v>-0.9709647999999995</v>
+      </c>
+      <c r="O92">
+        <v>-0.1941929599999999</v>
+      </c>
+      <c r="P92">
+        <v>-0.7767718399999997</v>
+      </c>
+      <c r="Q92">
+        <v>-0.3167718399999997</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>1.29404586953066</v>
+      </c>
+      <c r="T92">
+        <v>9.173287292922188</v>
+      </c>
+      <c r="U92">
+        <v>0.2138</v>
+      </c>
+      <c r="V92">
+        <v>0.1346363982501576</v>
+      </c>
+      <c r="W92">
+        <v>0.1850147380541163</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.6731819912507884</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2976678512017706</v>
+      </c>
+      <c r="C93">
+        <v>-5.270854888170319</v>
+      </c>
+      <c r="D93">
+        <v>8.663545111829681</v>
+      </c>
+      <c r="E93">
+        <v>10.3104</v>
+      </c>
+      <c r="F93">
+        <v>14.0504</v>
+      </c>
+      <c r="G93">
+        <v>0.116</v>
+      </c>
+      <c r="H93">
+        <v>11.7</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.46</v>
+      </c>
+      <c r="K93">
+        <v>0.46</v>
+      </c>
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>3.00397552</v>
+      </c>
+      <c r="N93">
+        <v>-1.00397552</v>
+      </c>
+      <c r="O93">
+        <v>-0.2007951039999999</v>
+      </c>
+      <c r="P93">
+        <v>-0.803180416</v>
+      </c>
+      <c r="Q93">
+        <v>-0.343180416</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>1.433517632811844</v>
+      </c>
+      <c r="T93">
+        <v>10.19254143658021</v>
+      </c>
+      <c r="U93">
+        <v>0.2138</v>
+      </c>
+      <c r="V93">
+        <v>0.1331568773902658</v>
+      </c>
+      <c r="W93">
+        <v>0.1853310596139612</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.6657843869513291</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2994178512017707</v>
+      </c>
+      <c r="C94">
+        <v>-5.483428969016241</v>
+      </c>
+      <c r="D94">
+        <v>8.605371030983759</v>
+      </c>
+      <c r="E94">
+        <v>10.4648</v>
+      </c>
+      <c r="F94">
+        <v>14.2048</v>
+      </c>
+      <c r="G94">
+        <v>0.116</v>
+      </c>
+      <c r="H94">
+        <v>11.7</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.46</v>
+      </c>
+      <c r="K94">
+        <v>0.46</v>
+      </c>
+      <c r="L94">
+        <v>2</v>
+      </c>
+      <c r="M94">
+        <v>3.03698624</v>
+      </c>
+      <c r="N94">
+        <v>-1.03698624</v>
+      </c>
+      <c r="O94">
+        <v>-0.207397248</v>
+      </c>
+      <c r="P94">
+        <v>-0.8295889920000001</v>
+      </c>
+      <c r="Q94">
+        <v>-0.3695889920000002</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>1.607857336913326</v>
+      </c>
+      <c r="T94">
+        <v>11.46660911615274</v>
+      </c>
+      <c r="U94">
+        <v>0.2138</v>
+      </c>
+      <c r="V94">
+        <v>0.1317095200273281</v>
+      </c>
+      <c r="W94">
+        <v>0.1856405046181572</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.6585476001366407</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3011678512017707</v>
+      </c>
+      <c r="C95">
+        <v>-5.695227004771166</v>
+      </c>
+      <c r="D95">
+        <v>8.547972995228834</v>
+      </c>
+      <c r="E95">
+        <v>10.6192</v>
+      </c>
+      <c r="F95">
+        <v>14.3592</v>
+      </c>
+      <c r="G95">
+        <v>0.116</v>
+      </c>
+      <c r="H95">
+        <v>11.7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.46</v>
+      </c>
+      <c r="K95">
+        <v>0.46</v>
+      </c>
+      <c r="L95">
+        <v>2</v>
+      </c>
+      <c r="M95">
+        <v>3.06999696</v>
+      </c>
+      <c r="N95">
+        <v>-1.06999696</v>
+      </c>
+      <c r="O95">
+        <v>-0.2139993919999999</v>
+      </c>
+      <c r="P95">
+        <v>-0.8559975679999998</v>
+      </c>
+      <c r="Q95">
+        <v>-0.3959975679999999</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.832008385043801</v>
+      </c>
+      <c r="T95">
+        <v>13.10469613274599</v>
+      </c>
+      <c r="U95">
+        <v>0.2138</v>
+      </c>
+      <c r="V95">
+        <v>0.1302932886291848</v>
+      </c>
+      <c r="W95">
+        <v>0.1859432948910803</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.6514664431459243</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3029178512017706</v>
+      </c>
+      <c r="C96">
+        <v>-5.906264421263783</v>
+      </c>
+      <c r="D96">
+        <v>8.491335578736217</v>
+      </c>
+      <c r="E96">
+        <v>10.7736</v>
+      </c>
+      <c r="F96">
+        <v>14.5136</v>
+      </c>
+      <c r="G96">
+        <v>0.116</v>
+      </c>
+      <c r="H96">
+        <v>11.7</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.46</v>
+      </c>
+      <c r="K96">
+        <v>0.46</v>
+      </c>
+      <c r="L96">
+        <v>2</v>
+      </c>
+      <c r="M96">
+        <v>3.10300768</v>
+      </c>
+      <c r="N96">
+        <v>-1.10300768</v>
+      </c>
+      <c r="O96">
+        <v>-0.2206015359999999</v>
+      </c>
+      <c r="P96">
+        <v>-0.8824061439999998</v>
+      </c>
+      <c r="Q96">
+        <v>-0.4224061439999999</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>2.130876449217769</v>
+      </c>
+      <c r="T96">
+        <v>15.28881215487032</v>
+      </c>
+      <c r="U96">
+        <v>0.2138</v>
+      </c>
+      <c r="V96">
+        <v>0.1289071898139807</v>
+      </c>
+      <c r="W96">
+        <v>0.1862396428177709</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.6445359490699037</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3046678512017707</v>
+      </c>
+      <c r="C97">
+        <v>-6.116556238178164</v>
+      </c>
+      <c r="D97">
+        <v>8.435443761821837</v>
+      </c>
+      <c r="E97">
+        <v>10.928</v>
+      </c>
+      <c r="F97">
+        <v>14.668</v>
+      </c>
+      <c r="G97">
+        <v>0.116</v>
+      </c>
+      <c r="H97">
+        <v>11.7</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.46</v>
+      </c>
+      <c r="K97">
+        <v>0.46</v>
+      </c>
+      <c r="L97">
+        <v>2</v>
+      </c>
+      <c r="M97">
+        <v>3.1360184</v>
+      </c>
+      <c r="N97">
+        <v>-1.1360184</v>
+      </c>
+      <c r="O97">
+        <v>-0.22720368</v>
+      </c>
+      <c r="P97">
+        <v>-0.9088147200000002</v>
+      </c>
+      <c r="Q97">
+        <v>-0.4488147200000002</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>2.549291739061324</v>
+      </c>
+      <c r="T97">
+        <v>18.3465745858444</v>
+      </c>
+      <c r="U97">
+        <v>0.2138</v>
+      </c>
+      <c r="V97">
+        <v>0.1275502720264651</v>
+      </c>
+      <c r="W97">
+        <v>0.1865297518407417</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.6377513601323257</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3064178512017707</v>
+      </c>
+      <c r="C98">
+        <v>-6.32611708233298</v>
+      </c>
+      <c r="D98">
+        <v>8.380282917667019</v>
+      </c>
+      <c r="E98">
+        <v>11.0824</v>
+      </c>
+      <c r="F98">
+        <v>14.8224</v>
+      </c>
+      <c r="G98">
+        <v>0.116</v>
+      </c>
+      <c r="H98">
+        <v>11.7</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.46</v>
+      </c>
+      <c r="K98">
+        <v>0.46</v>
+      </c>
+      <c r="L98">
+        <v>2</v>
+      </c>
+      <c r="M98">
+        <v>3.169029119999999</v>
+      </c>
+      <c r="N98">
+        <v>-1.169029119999999</v>
+      </c>
+      <c r="O98">
+        <v>-0.2338058239999998</v>
+      </c>
+      <c r="P98">
+        <v>-0.9352232959999995</v>
+      </c>
+      <c r="Q98">
+        <v>-0.4752232959999996</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>3.176914673826647</v>
+      </c>
+      <c r="T98">
+        <v>22.93321823230545</v>
+      </c>
+      <c r="U98">
+        <v>0.2138</v>
+      </c>
+      <c r="V98">
+        <v>0.1262216233595228</v>
+      </c>
+      <c r="W98">
+        <v>0.186813816925734</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.6311081167976141</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3081678512017707</v>
+      </c>
+      <c r="C99">
+        <v>-6.534961200443172</v>
+      </c>
+      <c r="D99">
+        <v>8.325838799556827</v>
+      </c>
+      <c r="E99">
+        <v>11.2368</v>
+      </c>
+      <c r="F99">
+        <v>14.9768</v>
+      </c>
+      <c r="G99">
+        <v>0.116</v>
+      </c>
+      <c r="H99">
+        <v>11.7</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.46</v>
+      </c>
+      <c r="K99">
+        <v>0.46</v>
+      </c>
+      <c r="L99">
+        <v>2</v>
+      </c>
+      <c r="M99">
+        <v>3.20203984</v>
+      </c>
+      <c r="N99">
+        <v>-1.20203984</v>
+      </c>
+      <c r="O99">
+        <v>-0.2404079679999999</v>
+      </c>
+      <c r="P99">
+        <v>-0.9616318719999999</v>
+      </c>
+      <c r="Q99">
+        <v>-0.5016318719999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>4.222952898435531</v>
+      </c>
+      <c r="T99">
+        <v>30.5776243097406</v>
+      </c>
+      <c r="U99">
+        <v>0.2138</v>
+      </c>
+      <c r="V99">
+        <v>0.1249203695104555</v>
+      </c>
+      <c r="W99">
+        <v>0.1870920249986646</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.6246018475522779</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3099178512017707</v>
+      </c>
+      <c r="C100">
+        <v>-6.743102471387299</v>
+      </c>
+      <c r="D100">
+        <v>8.272097528612701</v>
+      </c>
+      <c r="E100">
+        <v>11.3912</v>
+      </c>
+      <c r="F100">
+        <v>15.1312</v>
+      </c>
+      <c r="G100">
+        <v>0.116</v>
+      </c>
+      <c r="H100">
+        <v>11.7</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.46</v>
+      </c>
+      <c r="K100">
+        <v>0.46</v>
+      </c>
+      <c r="L100">
+        <v>2</v>
+      </c>
+      <c r="M100">
+        <v>3.23505056</v>
+      </c>
+      <c r="N100">
+        <v>-1.23505056</v>
+      </c>
+      <c r="O100">
+        <v>-0.2470101119999999</v>
+      </c>
+      <c r="P100">
+        <v>-0.988040448</v>
+      </c>
+      <c r="Q100">
+        <v>-0.5280404480000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>6.315029347653295</v>
+      </c>
+      <c r="T100">
+        <v>45.86643646461089</v>
+      </c>
+      <c r="U100">
+        <v>0.2138</v>
+      </c>
+      <c r="V100">
+        <v>0.1236456718623897</v>
+      </c>
+      <c r="W100">
+        <v>0.1873645553558211</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.6182283593119484</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3116678512017707</v>
+      </c>
+      <c r="C101">
+        <v>-6.950554418002906</v>
+      </c>
+      <c r="D101">
+        <v>8.219045581997094</v>
+      </c>
+      <c r="E101">
+        <v>11.5456</v>
+      </c>
+      <c r="F101">
+        <v>15.2856</v>
+      </c>
+      <c r="G101">
+        <v>0.116</v>
+      </c>
+      <c r="H101">
+        <v>11.7</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.46</v>
+      </c>
+      <c r="K101">
+        <v>0.46</v>
+      </c>
+      <c r="L101">
+        <v>2</v>
+      </c>
+      <c r="M101">
+        <v>3.26806128</v>
+      </c>
+      <c r="N101">
+        <v>-1.26806128</v>
+      </c>
+      <c r="O101">
+        <v>-0.2536122559999999</v>
+      </c>
+      <c r="P101">
+        <v>-1.014449024</v>
+      </c>
+      <c r="Q101">
+        <v>-0.5544490239999997</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>12.59125869530659</v>
+      </c>
+      <c r="T101">
+        <v>91.73287292922178</v>
+      </c>
+      <c r="U101">
+        <v>0.2138</v>
+      </c>
+      <c r="V101">
+        <v>0.1223967256819615</v>
+      </c>
+      <c r="W101">
+        <v>0.1876315800491966</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.6119836284098077</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
